--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/12,10,26 Останкино КИ и ЗПФ/дв 12,10,26 мррсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/12,10,26 Останкино КИ и ЗПФ/дв 12,10,26 мррсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\12,10,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14561D35-F9E3-4CC2-82EB-09AF034F46CC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B25210-1B77-456B-AB2B-12FF23A138B9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -502,8 +502,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0_ ;[Red]\-0\ "/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -633,7 +634,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -656,6 +657,9 @@
     <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -5142,7 +5146,8 @@
     <col min="22" max="23" width="6" customWidth="1"/>
     <col min="24" max="24" width="40.28515625" customWidth="1"/>
     <col min="25" max="25" width="7" customWidth="1"/>
-    <col min="26" max="50" width="3" customWidth="1"/>
+    <col min="26" max="26" width="6.5703125" style="24" customWidth="1"/>
+    <col min="27" max="50" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.25">
@@ -5171,7 +5176,7 @@
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
+      <c r="Z1" s="23"/>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
@@ -5223,7 +5228,7 @@
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" s="1"/>
+      <c r="Z2" s="23"/>
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
@@ -5325,7 +5330,7 @@
       <c r="Y3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="1"/>
+      <c r="Z3" s="23"/>
       <c r="AA3" s="1"/>
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
@@ -5389,7 +5394,7 @@
       </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
+      <c r="Z4" s="23"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
@@ -5483,7 +5488,7 @@
         <f>SUM(Y6:Y500)</f>
         <v>1362.6599999999999</v>
       </c>
-      <c r="Z5" s="1"/>
+      <c r="Z5" s="23"/>
       <c r="AA5" s="1"/>
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
@@ -5579,7 +5584,7 @@
         <f>G6*R6</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="1"/>
+      <c r="Z6" s="23"/>
       <c r="AA6" s="1"/>
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
@@ -5680,7 +5685,7 @@
         <f t="shared" ref="Y7:Y70" si="6">G7*R7</f>
         <v>32</v>
       </c>
-      <c r="Z7" s="1"/>
+      <c r="Z7" s="23"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
@@ -5753,7 +5758,7 @@
       </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="5">
-        <f t="shared" ref="R7:R70" si="7">ROUND(Q8,0)</f>
+        <f t="shared" ref="R8:R70" si="7">ROUND(Q8,0)</f>
         <v>0</v>
       </c>
       <c r="S8" s="20"/>
@@ -5778,7 +5783,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z8" s="1"/>
+      <c r="Z8" s="23"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
@@ -5879,7 +5884,7 @@
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="Z9" s="1"/>
+      <c r="Z9" s="23"/>
       <c r="AA9" s="1"/>
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
@@ -5975,7 +5980,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z10" s="1"/>
+      <c r="Z10" s="23"/>
       <c r="AA10" s="1"/>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
@@ -6076,7 +6081,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z11" s="1"/>
+      <c r="Z11" s="23"/>
       <c r="AA11" s="1"/>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
@@ -6170,7 +6175,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z12" s="1"/>
+      <c r="Z12" s="23"/>
       <c r="AA12" s="1"/>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
@@ -6269,7 +6274,7 @@
         <f t="shared" si="6"/>
         <v>203</v>
       </c>
-      <c r="Z13" s="1"/>
+      <c r="Z13" s="23"/>
       <c r="AA13" s="1"/>
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
@@ -6365,7 +6370,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z14" s="1"/>
+      <c r="Z14" s="23"/>
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
@@ -6459,7 +6464,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z15" s="1"/>
+      <c r="Z15" s="23"/>
       <c r="AA15" s="1"/>
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
@@ -6555,7 +6560,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z16" s="1"/>
+      <c r="Z16" s="23"/>
       <c r="AA16" s="1"/>
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
@@ -6651,7 +6656,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z17" s="1"/>
+      <c r="Z17" s="23"/>
       <c r="AA17" s="1"/>
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
@@ -6749,7 +6754,7 @@
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
-      <c r="Z18" s="1"/>
+      <c r="Z18" s="23"/>
       <c r="AA18" s="1"/>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
@@ -6848,7 +6853,7 @@
         <f t="shared" si="6"/>
         <v>14</v>
       </c>
-      <c r="Z19" s="1"/>
+      <c r="Z19" s="23"/>
       <c r="AA19" s="1"/>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
@@ -6942,7 +6947,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z20" s="1"/>
+      <c r="Z20" s="23"/>
       <c r="AA20" s="1"/>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
@@ -7038,7 +7043,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z21" s="1"/>
+      <c r="Z21" s="23"/>
       <c r="AA21" s="1"/>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
@@ -7131,14 +7136,14 @@
       <c r="W22" s="1">
         <v>28.8</v>
       </c>
-      <c r="X22" s="9" t="s">
+      <c r="X22" s="22" t="s">
         <v>147</v>
       </c>
       <c r="Y22" s="1">
         <f t="shared" si="6"/>
         <v>22</v>
       </c>
-      <c r="Z22" s="1"/>
+      <c r="Z22" s="23"/>
       <c r="AA22" s="1"/>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
@@ -7232,7 +7237,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z23" s="1"/>
+      <c r="Z23" s="23"/>
       <c r="AA23" s="1"/>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
@@ -7331,7 +7336,7 @@
         <f t="shared" si="6"/>
         <v>10</v>
       </c>
-      <c r="Z24" s="1"/>
+      <c r="Z24" s="23"/>
       <c r="AA24" s="1"/>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
@@ -7430,7 +7435,7 @@
         <f t="shared" si="6"/>
         <v>19.8</v>
       </c>
-      <c r="Z25" s="1"/>
+      <c r="Z25" s="23"/>
       <c r="AA25" s="1"/>
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
@@ -7526,7 +7531,7 @@
         <f t="shared" si="6"/>
         <v>2.6999999999999997</v>
       </c>
-      <c r="Z26" s="1"/>
+      <c r="Z26" s="23"/>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
@@ -7620,7 +7625,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z27" s="1"/>
+      <c r="Z27" s="23"/>
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
@@ -7718,7 +7723,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z28" s="1"/>
+      <c r="Z28" s="23"/>
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
@@ -7814,7 +7819,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z29" s="1"/>
+      <c r="Z29" s="23">
+        <f>69/E29</f>
+        <v>1.5</v>
+      </c>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
@@ -7913,7 +7921,7 @@
         <f t="shared" si="6"/>
         <v>59.2</v>
       </c>
-      <c r="Z30" s="1"/>
+      <c r="Z30" s="23"/>
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
@@ -8009,7 +8017,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z31" s="1"/>
+      <c r="Z31" s="23"/>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
@@ -8101,7 +8109,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z32" s="1"/>
+      <c r="Z32" s="23"/>
       <c r="AA32" s="1"/>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
@@ -8191,7 +8199,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z33" s="1"/>
+      <c r="Z33" s="23"/>
       <c r="AA33" s="1"/>
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
@@ -8291,7 +8299,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z34" s="1"/>
+      <c r="Z34" s="23"/>
       <c r="AA34" s="1"/>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
@@ -8389,7 +8397,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z35" s="1"/>
+      <c r="Z35" s="23"/>
       <c r="AA35" s="1"/>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
@@ -8487,7 +8495,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z36" s="1"/>
+      <c r="Z36" s="23"/>
       <c r="AA36" s="1"/>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
@@ -8585,7 +8593,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z37" s="1"/>
+      <c r="Z37" s="23"/>
       <c r="AA37" s="1"/>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
@@ -8681,7 +8689,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z38" s="1"/>
+      <c r="Z38" s="23"/>
       <c r="AA38" s="1"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
@@ -8780,7 +8788,7 @@
         <f t="shared" si="6"/>
         <v>73.2</v>
       </c>
-      <c r="Z39" s="1"/>
+      <c r="Z39" s="23"/>
       <c r="AA39" s="1"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
@@ -8872,7 +8880,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z40" s="1"/>
+      <c r="Z40" s="23"/>
       <c r="AA40" s="1"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
@@ -8970,7 +8978,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z41" s="1"/>
+      <c r="Z41" s="23"/>
       <c r="AA41" s="1"/>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
@@ -9066,7 +9074,10 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z42" s="1"/>
+      <c r="Z42" s="23">
+        <f>417/E42</f>
+        <v>1.4839857651245552</v>
+      </c>
       <c r="AA42" s="1"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
@@ -9164,7 +9175,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z43" s="1"/>
+      <c r="Z43" s="23"/>
       <c r="AA43" s="1"/>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
@@ -9263,7 +9274,7 @@
         <f t="shared" si="6"/>
         <v>20.91</v>
       </c>
-      <c r="Z44" s="1"/>
+      <c r="Z44" s="23"/>
       <c r="AA44" s="1"/>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
@@ -9360,7 +9371,7 @@
         <f t="shared" si="6"/>
         <v>24.84</v>
       </c>
-      <c r="Z45" s="1"/>
+      <c r="Z45" s="23"/>
       <c r="AA45" s="1"/>
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
@@ -9459,7 +9470,7 @@
         <f t="shared" si="6"/>
         <v>5.94</v>
       </c>
-      <c r="Z46" s="1"/>
+      <c r="Z46" s="23"/>
       <c r="AA46" s="1"/>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
@@ -9555,7 +9566,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z47" s="1"/>
+      <c r="Z47" s="23"/>
       <c r="AA47" s="1"/>
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
@@ -9647,7 +9658,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z48" s="1"/>
+      <c r="Z48" s="23"/>
       <c r="AA48" s="1"/>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
@@ -9744,7 +9755,7 @@
         <f t="shared" si="6"/>
         <v>97</v>
       </c>
-      <c r="Z49" s="1"/>
+      <c r="Z49" s="23"/>
       <c r="AA49" s="1"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
@@ -9840,7 +9851,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z50" s="1"/>
+      <c r="Z50" s="23"/>
       <c r="AA50" s="1"/>
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
@@ -9936,7 +9947,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z51" s="1"/>
+      <c r="Z51" s="23"/>
       <c r="AA51" s="1"/>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
@@ -10032,7 +10043,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z52" s="1"/>
+      <c r="Z52" s="23"/>
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
@@ -10120,7 +10131,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z53" s="1"/>
+      <c r="Z53" s="23"/>
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
@@ -10218,7 +10229,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z54" s="1"/>
+      <c r="Z54" s="23"/>
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
@@ -10316,7 +10327,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z55" s="1"/>
+      <c r="Z55" s="23"/>
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
       <c r="AC55" s="1"/>
@@ -10404,7 +10415,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z56" s="1"/>
+      <c r="Z56" s="23"/>
       <c r="AA56" s="1"/>
       <c r="AB56" s="1"/>
       <c r="AC56" s="1"/>
@@ -10503,7 +10514,7 @@
         <f t="shared" si="6"/>
         <v>6.3</v>
       </c>
-      <c r="Z57" s="1"/>
+      <c r="Z57" s="23"/>
       <c r="AA57" s="1"/>
       <c r="AB57" s="1"/>
       <c r="AC57" s="1"/>
@@ -10601,7 +10612,7 @@
         <f t="shared" si="6"/>
         <v>205</v>
       </c>
-      <c r="Z58" s="1"/>
+      <c r="Z58" s="23"/>
       <c r="AA58" s="1"/>
       <c r="AB58" s="1"/>
       <c r="AC58" s="1"/>
@@ -10700,7 +10711,7 @@
         <f t="shared" si="6"/>
         <v>43</v>
       </c>
-      <c r="Z59" s="1"/>
+      <c r="Z59" s="23"/>
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
@@ -10799,7 +10810,7 @@
         <f t="shared" si="6"/>
         <v>29.4</v>
       </c>
-      <c r="Z60" s="1"/>
+      <c r="Z60" s="23"/>
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
@@ -10891,7 +10902,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z61" s="1"/>
+      <c r="Z61" s="23"/>
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
@@ -10989,7 +11000,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z62" s="1"/>
+      <c r="Z62" s="23"/>
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
@@ -11088,7 +11099,7 @@
         <f t="shared" si="6"/>
         <v>16</v>
       </c>
-      <c r="Z63" s="1"/>
+      <c r="Z63" s="23"/>
       <c r="AA63" s="1"/>
       <c r="AB63" s="1"/>
       <c r="AC63" s="1"/>
@@ -11186,7 +11197,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z64" s="1"/>
+      <c r="Z64" s="23"/>
       <c r="AA64" s="1"/>
       <c r="AB64" s="1"/>
       <c r="AC64" s="1"/>
@@ -11285,7 +11296,7 @@
         <f t="shared" si="6"/>
         <v>17.099999999999998</v>
       </c>
-      <c r="Z65" s="1"/>
+      <c r="Z65" s="23"/>
       <c r="AA65" s="1"/>
       <c r="AB65" s="1"/>
       <c r="AC65" s="1"/>
@@ -11375,7 +11386,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z66" s="1"/>
+      <c r="Z66" s="23"/>
       <c r="AA66" s="1"/>
       <c r="AB66" s="1"/>
       <c r="AC66" s="1"/>
@@ -11461,7 +11472,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z67" s="1"/>
+      <c r="Z67" s="23"/>
       <c r="AA67" s="1"/>
       <c r="AB67" s="1"/>
       <c r="AC67" s="1"/>
@@ -11557,7 +11568,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z68" s="1"/>
+      <c r="Z68" s="23"/>
       <c r="AA68" s="1"/>
       <c r="AB68" s="1"/>
       <c r="AC68" s="1"/>
@@ -11643,7 +11654,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z69" s="1"/>
+      <c r="Z69" s="23"/>
       <c r="AA69" s="1"/>
       <c r="AB69" s="1"/>
       <c r="AC69" s="1"/>
@@ -11739,7 +11750,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z70" s="1"/>
+      <c r="Z70" s="23"/>
       <c r="AA70" s="1"/>
       <c r="AB70" s="1"/>
       <c r="AC70" s="1"/>
@@ -11835,7 +11846,7 @@
         <f t="shared" ref="Y71:Y109" si="19">G71*R71</f>
         <v>0</v>
       </c>
-      <c r="Z71" s="1"/>
+      <c r="Z71" s="23"/>
       <c r="AA71" s="1"/>
       <c r="AB71" s="1"/>
       <c r="AC71" s="1"/>
@@ -11931,7 +11942,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z72" s="1"/>
+      <c r="Z72" s="23"/>
       <c r="AA72" s="1"/>
       <c r="AB72" s="1"/>
       <c r="AC72" s="1"/>
@@ -12030,7 +12041,10 @@
         <f t="shared" si="19"/>
         <v>41.1</v>
       </c>
-      <c r="Z73" s="1"/>
+      <c r="Z73" s="23">
+        <f>P73/V73</f>
+        <v>1.4202898550724639</v>
+      </c>
       <c r="AA73" s="1"/>
       <c r="AB73" s="1"/>
       <c r="AC73" s="1"/>
@@ -12128,7 +12142,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z74" s="1"/>
+      <c r="Z74" s="23"/>
       <c r="AA74" s="1"/>
       <c r="AB74" s="1"/>
       <c r="AC74" s="1"/>
@@ -12227,7 +12241,7 @@
         <f t="shared" si="19"/>
         <v>9.5200000000000014</v>
       </c>
-      <c r="Z75" s="1"/>
+      <c r="Z75" s="23"/>
       <c r="AA75" s="1"/>
       <c r="AB75" s="1"/>
       <c r="AC75" s="1"/>
@@ -12323,7 +12337,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z76" s="1"/>
+      <c r="Z76" s="23"/>
       <c r="AA76" s="1"/>
       <c r="AB76" s="1"/>
       <c r="AC76" s="1"/>
@@ -12422,7 +12436,10 @@
         <f t="shared" si="19"/>
         <v>1.4000000000000001</v>
       </c>
-      <c r="Z77" s="1"/>
+      <c r="Z77" s="23">
+        <f>V77/W77</f>
+        <v>1.6974789915966386</v>
+      </c>
       <c r="AA77" s="1"/>
       <c r="AB77" s="1"/>
       <c r="AC77" s="1"/>
@@ -12518,7 +12535,10 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z78" s="1"/>
+      <c r="Z78" s="23">
+        <f>V78/W78</f>
+        <v>1.6839622641509435</v>
+      </c>
       <c r="AA78" s="1"/>
       <c r="AB78" s="1"/>
       <c r="AC78" s="1"/>
@@ -12610,7 +12630,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z79" s="1"/>
+      <c r="Z79" s="23"/>
       <c r="AA79" s="1"/>
       <c r="AB79" s="1"/>
       <c r="AC79" s="1"/>
@@ -12698,7 +12718,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z80" s="1"/>
+      <c r="Z80" s="23"/>
       <c r="AA80" s="1"/>
       <c r="AB80" s="1"/>
       <c r="AC80" s="1"/>
@@ -12792,7 +12812,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z81" s="1"/>
+      <c r="Z81" s="23"/>
       <c r="AA81" s="1"/>
       <c r="AB81" s="1"/>
       <c r="AC81" s="1"/>
@@ -12886,7 +12906,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z82" s="1"/>
+      <c r="Z82" s="23"/>
       <c r="AA82" s="1"/>
       <c r="AB82" s="1"/>
       <c r="AC82" s="1"/>
@@ -12985,7 +13005,7 @@
         <f t="shared" si="19"/>
         <v>14.76</v>
       </c>
-      <c r="Z83" s="1"/>
+      <c r="Z83" s="23"/>
       <c r="AA83" s="1"/>
       <c r="AB83" s="1"/>
       <c r="AC83" s="1"/>
@@ -13077,7 +13097,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z84" s="1"/>
+      <c r="Z84" s="23"/>
       <c r="AA84" s="1"/>
       <c r="AB84" s="1"/>
       <c r="AC84" s="1"/>
@@ -13174,7 +13194,7 @@
         <f t="shared" si="19"/>
         <v>5.7</v>
       </c>
-      <c r="Z85" s="1"/>
+      <c r="Z85" s="23"/>
       <c r="AA85" s="1"/>
       <c r="AB85" s="1"/>
       <c r="AC85" s="1"/>
@@ -13273,7 +13293,7 @@
         <f t="shared" si="19"/>
         <v>21.12</v>
       </c>
-      <c r="Z86" s="1"/>
+      <c r="Z86" s="23"/>
       <c r="AA86" s="1"/>
       <c r="AB86" s="1"/>
       <c r="AC86" s="1"/>
@@ -13365,7 +13385,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z87" s="1"/>
+      <c r="Z87" s="23"/>
       <c r="AA87" s="1"/>
       <c r="AB87" s="1"/>
       <c r="AC87" s="1"/>
@@ -13459,7 +13479,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z88" s="1"/>
+      <c r="Z88" s="23"/>
       <c r="AA88" s="1"/>
       <c r="AB88" s="1"/>
       <c r="AC88" s="1"/>
@@ -13556,7 +13576,7 @@
         <f t="shared" si="19"/>
         <v>59.02</v>
       </c>
-      <c r="Z89" s="1"/>
+      <c r="Z89" s="23"/>
       <c r="AA89" s="1"/>
       <c r="AB89" s="1"/>
       <c r="AC89" s="1"/>
@@ -13653,7 +13673,7 @@
         <f t="shared" si="19"/>
         <v>88</v>
       </c>
-      <c r="Z90" s="1"/>
+      <c r="Z90" s="23"/>
       <c r="AA90" s="1"/>
       <c r="AB90" s="1"/>
       <c r="AC90" s="1"/>
@@ -13750,7 +13770,7 @@
         <f t="shared" si="19"/>
         <v>1.55</v>
       </c>
-      <c r="Z91" s="1"/>
+      <c r="Z91" s="23"/>
       <c r="AA91" s="1"/>
       <c r="AB91" s="1"/>
       <c r="AC91" s="1"/>
@@ -13844,7 +13864,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z92" s="1"/>
+      <c r="Z92" s="23"/>
       <c r="AA92" s="1"/>
       <c r="AB92" s="1"/>
       <c r="AC92" s="1"/>
@@ -13943,7 +13963,7 @@
         <f t="shared" si="19"/>
         <v>52.800000000000004</v>
       </c>
-      <c r="Z93" s="1"/>
+      <c r="Z93" s="23"/>
       <c r="AA93" s="1"/>
       <c r="AB93" s="1"/>
       <c r="AC93" s="1"/>
@@ -14039,7 +14059,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z94" s="1"/>
+      <c r="Z94" s="23"/>
       <c r="AA94" s="1"/>
       <c r="AB94" s="1"/>
       <c r="AC94" s="1"/>
@@ -14137,7 +14157,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z95" s="1"/>
+      <c r="Z95" s="23"/>
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
       <c r="AC95" s="1"/>
@@ -14229,7 +14249,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z96" s="1"/>
+      <c r="Z96" s="23"/>
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
       <c r="AC96" s="1"/>
@@ -14326,7 +14346,7 @@
         <f t="shared" si="19"/>
         <v>36.300000000000004</v>
       </c>
-      <c r="Z97" s="1"/>
+      <c r="Z97" s="23"/>
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
       <c r="AC97" s="1"/>
@@ -14425,7 +14445,7 @@
         <f t="shared" si="19"/>
         <v>33.300000000000004</v>
       </c>
-      <c r="Z98" s="1"/>
+      <c r="Z98" s="23"/>
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
       <c r="AC98" s="1"/>
@@ -14522,7 +14542,7 @@
         <f t="shared" si="19"/>
         <v>37.200000000000003</v>
       </c>
-      <c r="Z99" s="1"/>
+      <c r="Z99" s="23"/>
       <c r="AA99" s="1"/>
       <c r="AB99" s="1"/>
       <c r="AC99" s="1"/>
@@ -14616,7 +14636,10 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z100" s="1"/>
+      <c r="Z100" s="23">
+        <f>V100/W100</f>
+        <v>2.043010752688172</v>
+      </c>
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
       <c r="AC100" s="1"/>
@@ -14708,7 +14731,7 @@
         <f t="shared" si="19"/>
         <v>2.5</v>
       </c>
-      <c r="Z101" s="1"/>
+      <c r="Z101" s="23"/>
       <c r="AA101" s="1"/>
       <c r="AB101" s="1"/>
       <c r="AC101" s="1"/>
@@ -14802,7 +14825,7 @@
         <f t="shared" si="19"/>
         <v>3</v>
       </c>
-      <c r="Z102" s="1"/>
+      <c r="Z102" s="23"/>
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
       <c r="AC102" s="1"/>
@@ -14898,7 +14921,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z103" s="1"/>
+      <c r="Z103" s="23"/>
       <c r="AA103" s="1"/>
       <c r="AB103" s="1"/>
       <c r="AC103" s="1"/>
@@ -14997,7 +15020,7 @@
         <f t="shared" si="19"/>
         <v>24</v>
       </c>
-      <c r="Z104" s="1"/>
+      <c r="Z104" s="23"/>
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
       <c r="AC104" s="1"/>
@@ -15085,7 +15108,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z105" s="1"/>
+      <c r="Z105" s="23"/>
       <c r="AA105" s="1"/>
       <c r="AB105" s="1"/>
       <c r="AC105" s="1"/>
@@ -15171,7 +15194,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z106" s="1"/>
+      <c r="Z106" s="23"/>
       <c r="AA106" s="1"/>
       <c r="AB106" s="1"/>
       <c r="AC106" s="1"/>
@@ -15252,7 +15275,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z107" s="1"/>
+      <c r="Z107" s="23"/>
       <c r="AA107" s="1"/>
       <c r="AB107" s="1"/>
       <c r="AC107" s="1"/>
@@ -15333,7 +15356,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z108" s="1"/>
+      <c r="Z108" s="23"/>
       <c r="AA108" s="1"/>
       <c r="AB108" s="1"/>
       <c r="AC108" s="1"/>
@@ -15414,7 +15437,7 @@
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Z109" s="1"/>
+      <c r="Z109" s="23"/>
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
       <c r="AC109" s="1"/>
@@ -15466,7 +15489,7 @@
       <c r="W110" s="1"/>
       <c r="X110" s="1"/>
       <c r="Y110" s="1"/>
-      <c r="Z110" s="1"/>
+      <c r="Z110" s="23"/>
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
       <c r="AC110" s="1"/>
@@ -15518,7 +15541,7 @@
       <c r="W111" s="1"/>
       <c r="X111" s="1"/>
       <c r="Y111" s="1"/>
-      <c r="Z111" s="1"/>
+      <c r="Z111" s="23"/>
       <c r="AA111" s="1"/>
       <c r="AB111" s="1"/>
       <c r="AC111" s="1"/>
@@ -15570,7 +15593,7 @@
       <c r="W112" s="1"/>
       <c r="X112" s="1"/>
       <c r="Y112" s="1"/>
-      <c r="Z112" s="1"/>
+      <c r="Z112" s="23"/>
       <c r="AA112" s="1"/>
       <c r="AB112" s="1"/>
       <c r="AC112" s="1"/>
@@ -15622,7 +15645,7 @@
       <c r="W113" s="1"/>
       <c r="X113" s="1"/>
       <c r="Y113" s="1"/>
-      <c r="Z113" s="1"/>
+      <c r="Z113" s="23"/>
       <c r="AA113" s="1"/>
       <c r="AB113" s="1"/>
       <c r="AC113" s="1"/>
@@ -15674,7 +15697,7 @@
       <c r="W114" s="1"/>
       <c r="X114" s="1"/>
       <c r="Y114" s="1"/>
-      <c r="Z114" s="1"/>
+      <c r="Z114" s="23"/>
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
       <c r="AC114" s="1"/>
@@ -15726,7 +15749,7 @@
       <c r="W115" s="1"/>
       <c r="X115" s="1"/>
       <c r="Y115" s="1"/>
-      <c r="Z115" s="1"/>
+      <c r="Z115" s="23"/>
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
       <c r="AC115" s="1"/>
@@ -15778,7 +15801,7 @@
       <c r="W116" s="1"/>
       <c r="X116" s="1"/>
       <c r="Y116" s="1"/>
-      <c r="Z116" s="1"/>
+      <c r="Z116" s="23"/>
       <c r="AA116" s="1"/>
       <c r="AB116" s="1"/>
       <c r="AC116" s="1"/>
@@ -15830,7 +15853,7 @@
       <c r="W117" s="1"/>
       <c r="X117" s="1"/>
       <c r="Y117" s="1"/>
-      <c r="Z117" s="1"/>
+      <c r="Z117" s="23"/>
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
       <c r="AC117" s="1"/>
@@ -15882,7 +15905,7 @@
       <c r="W118" s="1"/>
       <c r="X118" s="1"/>
       <c r="Y118" s="1"/>
-      <c r="Z118" s="1"/>
+      <c r="Z118" s="23"/>
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
       <c r="AC118" s="1"/>
@@ -15934,7 +15957,7 @@
       <c r="W119" s="1"/>
       <c r="X119" s="1"/>
       <c r="Y119" s="1"/>
-      <c r="Z119" s="1"/>
+      <c r="Z119" s="23"/>
       <c r="AA119" s="1"/>
       <c r="AB119" s="1"/>
       <c r="AC119" s="1"/>
@@ -15986,7 +16009,7 @@
       <c r="W120" s="1"/>
       <c r="X120" s="1"/>
       <c r="Y120" s="1"/>
-      <c r="Z120" s="1"/>
+      <c r="Z120" s="23"/>
       <c r="AA120" s="1"/>
       <c r="AB120" s="1"/>
       <c r="AC120" s="1"/>
@@ -16038,7 +16061,7 @@
       <c r="W121" s="1"/>
       <c r="X121" s="1"/>
       <c r="Y121" s="1"/>
-      <c r="Z121" s="1"/>
+      <c r="Z121" s="23"/>
       <c r="AA121" s="1"/>
       <c r="AB121" s="1"/>
       <c r="AC121" s="1"/>
@@ -16090,7 +16113,7 @@
       <c r="W122" s="1"/>
       <c r="X122" s="1"/>
       <c r="Y122" s="1"/>
-      <c r="Z122" s="1"/>
+      <c r="Z122" s="23"/>
       <c r="AA122" s="1"/>
       <c r="AB122" s="1"/>
       <c r="AC122" s="1"/>
@@ -16142,7 +16165,7 @@
       <c r="W123" s="1"/>
       <c r="X123" s="1"/>
       <c r="Y123" s="1"/>
-      <c r="Z123" s="1"/>
+      <c r="Z123" s="23"/>
       <c r="AA123" s="1"/>
       <c r="AB123" s="1"/>
       <c r="AC123" s="1"/>
@@ -16194,7 +16217,7 @@
       <c r="W124" s="1"/>
       <c r="X124" s="1"/>
       <c r="Y124" s="1"/>
-      <c r="Z124" s="1"/>
+      <c r="Z124" s="23"/>
       <c r="AA124" s="1"/>
       <c r="AB124" s="1"/>
       <c r="AC124" s="1"/>
@@ -16246,7 +16269,7 @@
       <c r="W125" s="1"/>
       <c r="X125" s="1"/>
       <c r="Y125" s="1"/>
-      <c r="Z125" s="1"/>
+      <c r="Z125" s="23"/>
       <c r="AA125" s="1"/>
       <c r="AB125" s="1"/>
       <c r="AC125" s="1"/>
@@ -16298,7 +16321,7 @@
       <c r="W126" s="1"/>
       <c r="X126" s="1"/>
       <c r="Y126" s="1"/>
-      <c r="Z126" s="1"/>
+      <c r="Z126" s="23"/>
       <c r="AA126" s="1"/>
       <c r="AB126" s="1"/>
       <c r="AC126" s="1"/>
@@ -16350,7 +16373,7 @@
       <c r="W127" s="1"/>
       <c r="X127" s="1"/>
       <c r="Y127" s="1"/>
-      <c r="Z127" s="1"/>
+      <c r="Z127" s="23"/>
       <c r="AA127" s="1"/>
       <c r="AB127" s="1"/>
       <c r="AC127" s="1"/>
@@ -16402,7 +16425,7 @@
       <c r="W128" s="1"/>
       <c r="X128" s="1"/>
       <c r="Y128" s="1"/>
-      <c r="Z128" s="1"/>
+      <c r="Z128" s="23"/>
       <c r="AA128" s="1"/>
       <c r="AB128" s="1"/>
       <c r="AC128" s="1"/>
@@ -16454,7 +16477,7 @@
       <c r="W129" s="1"/>
       <c r="X129" s="1"/>
       <c r="Y129" s="1"/>
-      <c r="Z129" s="1"/>
+      <c r="Z129" s="23"/>
       <c r="AA129" s="1"/>
       <c r="AB129" s="1"/>
       <c r="AC129" s="1"/>
@@ -16506,7 +16529,7 @@
       <c r="W130" s="1"/>
       <c r="X130" s="1"/>
       <c r="Y130" s="1"/>
-      <c r="Z130" s="1"/>
+      <c r="Z130" s="23"/>
       <c r="AA130" s="1"/>
       <c r="AB130" s="1"/>
       <c r="AC130" s="1"/>
@@ -16558,7 +16581,7 @@
       <c r="W131" s="1"/>
       <c r="X131" s="1"/>
       <c r="Y131" s="1"/>
-      <c r="Z131" s="1"/>
+      <c r="Z131" s="23"/>
       <c r="AA131" s="1"/>
       <c r="AB131" s="1"/>
       <c r="AC131" s="1"/>
@@ -16610,7 +16633,7 @@
       <c r="W132" s="1"/>
       <c r="X132" s="1"/>
       <c r="Y132" s="1"/>
-      <c r="Z132" s="1"/>
+      <c r="Z132" s="23"/>
       <c r="AA132" s="1"/>
       <c r="AB132" s="1"/>
       <c r="AC132" s="1"/>
@@ -16662,7 +16685,7 @@
       <c r="W133" s="1"/>
       <c r="X133" s="1"/>
       <c r="Y133" s="1"/>
-      <c r="Z133" s="1"/>
+      <c r="Z133" s="23"/>
       <c r="AA133" s="1"/>
       <c r="AB133" s="1"/>
       <c r="AC133" s="1"/>
@@ -16714,7 +16737,7 @@
       <c r="W134" s="1"/>
       <c r="X134" s="1"/>
       <c r="Y134" s="1"/>
-      <c r="Z134" s="1"/>
+      <c r="Z134" s="23"/>
       <c r="AA134" s="1"/>
       <c r="AB134" s="1"/>
       <c r="AC134" s="1"/>
@@ -16766,7 +16789,7 @@
       <c r="W135" s="1"/>
       <c r="X135" s="1"/>
       <c r="Y135" s="1"/>
-      <c r="Z135" s="1"/>
+      <c r="Z135" s="23"/>
       <c r="AA135" s="1"/>
       <c r="AB135" s="1"/>
       <c r="AC135" s="1"/>
@@ -16818,7 +16841,7 @@
       <c r="W136" s="1"/>
       <c r="X136" s="1"/>
       <c r="Y136" s="1"/>
-      <c r="Z136" s="1"/>
+      <c r="Z136" s="23"/>
       <c r="AA136" s="1"/>
       <c r="AB136" s="1"/>
       <c r="AC136" s="1"/>
@@ -16870,7 +16893,7 @@
       <c r="W137" s="1"/>
       <c r="X137" s="1"/>
       <c r="Y137" s="1"/>
-      <c r="Z137" s="1"/>
+      <c r="Z137" s="23"/>
       <c r="AA137" s="1"/>
       <c r="AB137" s="1"/>
       <c r="AC137" s="1"/>
@@ -16922,7 +16945,7 @@
       <c r="W138" s="1"/>
       <c r="X138" s="1"/>
       <c r="Y138" s="1"/>
-      <c r="Z138" s="1"/>
+      <c r="Z138" s="23"/>
       <c r="AA138" s="1"/>
       <c r="AB138" s="1"/>
       <c r="AC138" s="1"/>
@@ -16974,7 +16997,7 @@
       <c r="W139" s="1"/>
       <c r="X139" s="1"/>
       <c r="Y139" s="1"/>
-      <c r="Z139" s="1"/>
+      <c r="Z139" s="23"/>
       <c r="AA139" s="1"/>
       <c r="AB139" s="1"/>
       <c r="AC139" s="1"/>
@@ -17026,7 +17049,7 @@
       <c r="W140" s="1"/>
       <c r="X140" s="1"/>
       <c r="Y140" s="1"/>
-      <c r="Z140" s="1"/>
+      <c r="Z140" s="23"/>
       <c r="AA140" s="1"/>
       <c r="AB140" s="1"/>
       <c r="AC140" s="1"/>
@@ -17078,7 +17101,7 @@
       <c r="W141" s="1"/>
       <c r="X141" s="1"/>
       <c r="Y141" s="1"/>
-      <c r="Z141" s="1"/>
+      <c r="Z141" s="23"/>
       <c r="AA141" s="1"/>
       <c r="AB141" s="1"/>
       <c r="AC141" s="1"/>
@@ -17130,7 +17153,7 @@
       <c r="W142" s="1"/>
       <c r="X142" s="1"/>
       <c r="Y142" s="1"/>
-      <c r="Z142" s="1"/>
+      <c r="Z142" s="23"/>
       <c r="AA142" s="1"/>
       <c r="AB142" s="1"/>
       <c r="AC142" s="1"/>
@@ -17182,7 +17205,7 @@
       <c r="W143" s="1"/>
       <c r="X143" s="1"/>
       <c r="Y143" s="1"/>
-      <c r="Z143" s="1"/>
+      <c r="Z143" s="23"/>
       <c r="AA143" s="1"/>
       <c r="AB143" s="1"/>
       <c r="AC143" s="1"/>
@@ -17234,7 +17257,7 @@
       <c r="W144" s="1"/>
       <c r="X144" s="1"/>
       <c r="Y144" s="1"/>
-      <c r="Z144" s="1"/>
+      <c r="Z144" s="23"/>
       <c r="AA144" s="1"/>
       <c r="AB144" s="1"/>
       <c r="AC144" s="1"/>
@@ -17286,7 +17309,7 @@
       <c r="W145" s="1"/>
       <c r="X145" s="1"/>
       <c r="Y145" s="1"/>
-      <c r="Z145" s="1"/>
+      <c r="Z145" s="23"/>
       <c r="AA145" s="1"/>
       <c r="AB145" s="1"/>
       <c r="AC145" s="1"/>
@@ -17338,7 +17361,7 @@
       <c r="W146" s="1"/>
       <c r="X146" s="1"/>
       <c r="Y146" s="1"/>
-      <c r="Z146" s="1"/>
+      <c r="Z146" s="23"/>
       <c r="AA146" s="1"/>
       <c r="AB146" s="1"/>
       <c r="AC146" s="1"/>
@@ -17390,7 +17413,7 @@
       <c r="W147" s="1"/>
       <c r="X147" s="1"/>
       <c r="Y147" s="1"/>
-      <c r="Z147" s="1"/>
+      <c r="Z147" s="23"/>
       <c r="AA147" s="1"/>
       <c r="AB147" s="1"/>
       <c r="AC147" s="1"/>
@@ -17442,7 +17465,7 @@
       <c r="W148" s="1"/>
       <c r="X148" s="1"/>
       <c r="Y148" s="1"/>
-      <c r="Z148" s="1"/>
+      <c r="Z148" s="23"/>
       <c r="AA148" s="1"/>
       <c r="AB148" s="1"/>
       <c r="AC148" s="1"/>
@@ -17494,7 +17517,7 @@
       <c r="W149" s="1"/>
       <c r="X149" s="1"/>
       <c r="Y149" s="1"/>
-      <c r="Z149" s="1"/>
+      <c r="Z149" s="23"/>
       <c r="AA149" s="1"/>
       <c r="AB149" s="1"/>
       <c r="AC149" s="1"/>
@@ -17546,7 +17569,7 @@
       <c r="W150" s="1"/>
       <c r="X150" s="1"/>
       <c r="Y150" s="1"/>
-      <c r="Z150" s="1"/>
+      <c r="Z150" s="23"/>
       <c r="AA150" s="1"/>
       <c r="AB150" s="1"/>
       <c r="AC150" s="1"/>
@@ -17598,7 +17621,7 @@
       <c r="W151" s="1"/>
       <c r="X151" s="1"/>
       <c r="Y151" s="1"/>
-      <c r="Z151" s="1"/>
+      <c r="Z151" s="23"/>
       <c r="AA151" s="1"/>
       <c r="AB151" s="1"/>
       <c r="AC151" s="1"/>
@@ -17650,7 +17673,7 @@
       <c r="W152" s="1"/>
       <c r="X152" s="1"/>
       <c r="Y152" s="1"/>
-      <c r="Z152" s="1"/>
+      <c r="Z152" s="23"/>
       <c r="AA152" s="1"/>
       <c r="AB152" s="1"/>
       <c r="AC152" s="1"/>
@@ -17702,7 +17725,7 @@
       <c r="W153" s="1"/>
       <c r="X153" s="1"/>
       <c r="Y153" s="1"/>
-      <c r="Z153" s="1"/>
+      <c r="Z153" s="23"/>
       <c r="AA153" s="1"/>
       <c r="AB153" s="1"/>
       <c r="AC153" s="1"/>
@@ -17754,7 +17777,7 @@
       <c r="W154" s="1"/>
       <c r="X154" s="1"/>
       <c r="Y154" s="1"/>
-      <c r="Z154" s="1"/>
+      <c r="Z154" s="23"/>
       <c r="AA154" s="1"/>
       <c r="AB154" s="1"/>
       <c r="AC154" s="1"/>
@@ -17806,7 +17829,7 @@
       <c r="W155" s="1"/>
       <c r="X155" s="1"/>
       <c r="Y155" s="1"/>
-      <c r="Z155" s="1"/>
+      <c r="Z155" s="23"/>
       <c r="AA155" s="1"/>
       <c r="AB155" s="1"/>
       <c r="AC155" s="1"/>
@@ -17858,7 +17881,7 @@
       <c r="W156" s="1"/>
       <c r="X156" s="1"/>
       <c r="Y156" s="1"/>
-      <c r="Z156" s="1"/>
+      <c r="Z156" s="23"/>
       <c r="AA156" s="1"/>
       <c r="AB156" s="1"/>
       <c r="AC156" s="1"/>
@@ -17910,7 +17933,7 @@
       <c r="W157" s="1"/>
       <c r="X157" s="1"/>
       <c r="Y157" s="1"/>
-      <c r="Z157" s="1"/>
+      <c r="Z157" s="23"/>
       <c r="AA157" s="1"/>
       <c r="AB157" s="1"/>
       <c r="AC157" s="1"/>
@@ -17962,7 +17985,7 @@
       <c r="W158" s="1"/>
       <c r="X158" s="1"/>
       <c r="Y158" s="1"/>
-      <c r="Z158" s="1"/>
+      <c r="Z158" s="23"/>
       <c r="AA158" s="1"/>
       <c r="AB158" s="1"/>
       <c r="AC158" s="1"/>
@@ -18014,7 +18037,7 @@
       <c r="W159" s="1"/>
       <c r="X159" s="1"/>
       <c r="Y159" s="1"/>
-      <c r="Z159" s="1"/>
+      <c r="Z159" s="23"/>
       <c r="AA159" s="1"/>
       <c r="AB159" s="1"/>
       <c r="AC159" s="1"/>
@@ -18066,7 +18089,7 @@
       <c r="W160" s="1"/>
       <c r="X160" s="1"/>
       <c r="Y160" s="1"/>
-      <c r="Z160" s="1"/>
+      <c r="Z160" s="23"/>
       <c r="AA160" s="1"/>
       <c r="AB160" s="1"/>
       <c r="AC160" s="1"/>
@@ -18118,7 +18141,7 @@
       <c r="W161" s="1"/>
       <c r="X161" s="1"/>
       <c r="Y161" s="1"/>
-      <c r="Z161" s="1"/>
+      <c r="Z161" s="23"/>
       <c r="AA161" s="1"/>
       <c r="AB161" s="1"/>
       <c r="AC161" s="1"/>
@@ -18170,7 +18193,7 @@
       <c r="W162" s="1"/>
       <c r="X162" s="1"/>
       <c r="Y162" s="1"/>
-      <c r="Z162" s="1"/>
+      <c r="Z162" s="23"/>
       <c r="AA162" s="1"/>
       <c r="AB162" s="1"/>
       <c r="AC162" s="1"/>
@@ -18222,7 +18245,7 @@
       <c r="W163" s="1"/>
       <c r="X163" s="1"/>
       <c r="Y163" s="1"/>
-      <c r="Z163" s="1"/>
+      <c r="Z163" s="23"/>
       <c r="AA163" s="1"/>
       <c r="AB163" s="1"/>
       <c r="AC163" s="1"/>
@@ -18274,7 +18297,7 @@
       <c r="W164" s="1"/>
       <c r="X164" s="1"/>
       <c r="Y164" s="1"/>
-      <c r="Z164" s="1"/>
+      <c r="Z164" s="23"/>
       <c r="AA164" s="1"/>
       <c r="AB164" s="1"/>
       <c r="AC164" s="1"/>
@@ -18326,7 +18349,7 @@
       <c r="W165" s="1"/>
       <c r="X165" s="1"/>
       <c r="Y165" s="1"/>
-      <c r="Z165" s="1"/>
+      <c r="Z165" s="23"/>
       <c r="AA165" s="1"/>
       <c r="AB165" s="1"/>
       <c r="AC165" s="1"/>
@@ -18378,7 +18401,7 @@
       <c r="W166" s="1"/>
       <c r="X166" s="1"/>
       <c r="Y166" s="1"/>
-      <c r="Z166" s="1"/>
+      <c r="Z166" s="23"/>
       <c r="AA166" s="1"/>
       <c r="AB166" s="1"/>
       <c r="AC166" s="1"/>
@@ -18430,7 +18453,7 @@
       <c r="W167" s="1"/>
       <c r="X167" s="1"/>
       <c r="Y167" s="1"/>
-      <c r="Z167" s="1"/>
+      <c r="Z167" s="23"/>
       <c r="AA167" s="1"/>
       <c r="AB167" s="1"/>
       <c r="AC167" s="1"/>
@@ -18482,7 +18505,7 @@
       <c r="W168" s="1"/>
       <c r="X168" s="1"/>
       <c r="Y168" s="1"/>
-      <c r="Z168" s="1"/>
+      <c r="Z168" s="23"/>
       <c r="AA168" s="1"/>
       <c r="AB168" s="1"/>
       <c r="AC168" s="1"/>
@@ -18534,7 +18557,7 @@
       <c r="W169" s="1"/>
       <c r="X169" s="1"/>
       <c r="Y169" s="1"/>
-      <c r="Z169" s="1"/>
+      <c r="Z169" s="23"/>
       <c r="AA169" s="1"/>
       <c r="AB169" s="1"/>
       <c r="AC169" s="1"/>
@@ -18586,7 +18609,7 @@
       <c r="W170" s="1"/>
       <c r="X170" s="1"/>
       <c r="Y170" s="1"/>
-      <c r="Z170" s="1"/>
+      <c r="Z170" s="23"/>
       <c r="AA170" s="1"/>
       <c r="AB170" s="1"/>
       <c r="AC170" s="1"/>
@@ -18638,7 +18661,7 @@
       <c r="W171" s="1"/>
       <c r="X171" s="1"/>
       <c r="Y171" s="1"/>
-      <c r="Z171" s="1"/>
+      <c r="Z171" s="23"/>
       <c r="AA171" s="1"/>
       <c r="AB171" s="1"/>
       <c r="AC171" s="1"/>
@@ -18690,7 +18713,7 @@
       <c r="W172" s="1"/>
       <c r="X172" s="1"/>
       <c r="Y172" s="1"/>
-      <c r="Z172" s="1"/>
+      <c r="Z172" s="23"/>
       <c r="AA172" s="1"/>
       <c r="AB172" s="1"/>
       <c r="AC172" s="1"/>
@@ -18742,7 +18765,7 @@
       <c r="W173" s="1"/>
       <c r="X173" s="1"/>
       <c r="Y173" s="1"/>
-      <c r="Z173" s="1"/>
+      <c r="Z173" s="23"/>
       <c r="AA173" s="1"/>
       <c r="AB173" s="1"/>
       <c r="AC173" s="1"/>
@@ -18794,7 +18817,7 @@
       <c r="W174" s="1"/>
       <c r="X174" s="1"/>
       <c r="Y174" s="1"/>
-      <c r="Z174" s="1"/>
+      <c r="Z174" s="23"/>
       <c r="AA174" s="1"/>
       <c r="AB174" s="1"/>
       <c r="AC174" s="1"/>
@@ -18846,7 +18869,7 @@
       <c r="W175" s="1"/>
       <c r="X175" s="1"/>
       <c r="Y175" s="1"/>
-      <c r="Z175" s="1"/>
+      <c r="Z175" s="23"/>
       <c r="AA175" s="1"/>
       <c r="AB175" s="1"/>
       <c r="AC175" s="1"/>
@@ -18898,7 +18921,7 @@
       <c r="W176" s="1"/>
       <c r="X176" s="1"/>
       <c r="Y176" s="1"/>
-      <c r="Z176" s="1"/>
+      <c r="Z176" s="23"/>
       <c r="AA176" s="1"/>
       <c r="AB176" s="1"/>
       <c r="AC176" s="1"/>
@@ -18950,7 +18973,7 @@
       <c r="W177" s="1"/>
       <c r="X177" s="1"/>
       <c r="Y177" s="1"/>
-      <c r="Z177" s="1"/>
+      <c r="Z177" s="23"/>
       <c r="AA177" s="1"/>
       <c r="AB177" s="1"/>
       <c r="AC177" s="1"/>
@@ -19002,7 +19025,7 @@
       <c r="W178" s="1"/>
       <c r="X178" s="1"/>
       <c r="Y178" s="1"/>
-      <c r="Z178" s="1"/>
+      <c r="Z178" s="23"/>
       <c r="AA178" s="1"/>
       <c r="AB178" s="1"/>
       <c r="AC178" s="1"/>
@@ -19054,7 +19077,7 @@
       <c r="W179" s="1"/>
       <c r="X179" s="1"/>
       <c r="Y179" s="1"/>
-      <c r="Z179" s="1"/>
+      <c r="Z179" s="23"/>
       <c r="AA179" s="1"/>
       <c r="AB179" s="1"/>
       <c r="AC179" s="1"/>
@@ -19106,7 +19129,7 @@
       <c r="W180" s="1"/>
       <c r="X180" s="1"/>
       <c r="Y180" s="1"/>
-      <c r="Z180" s="1"/>
+      <c r="Z180" s="23"/>
       <c r="AA180" s="1"/>
       <c r="AB180" s="1"/>
       <c r="AC180" s="1"/>
@@ -19158,7 +19181,7 @@
       <c r="W181" s="1"/>
       <c r="X181" s="1"/>
       <c r="Y181" s="1"/>
-      <c r="Z181" s="1"/>
+      <c r="Z181" s="23"/>
       <c r="AA181" s="1"/>
       <c r="AB181" s="1"/>
       <c r="AC181" s="1"/>
@@ -19210,7 +19233,7 @@
       <c r="W182" s="1"/>
       <c r="X182" s="1"/>
       <c r="Y182" s="1"/>
-      <c r="Z182" s="1"/>
+      <c r="Z182" s="23"/>
       <c r="AA182" s="1"/>
       <c r="AB182" s="1"/>
       <c r="AC182" s="1"/>
@@ -19262,7 +19285,7 @@
       <c r="W183" s="1"/>
       <c r="X183" s="1"/>
       <c r="Y183" s="1"/>
-      <c r="Z183" s="1"/>
+      <c r="Z183" s="23"/>
       <c r="AA183" s="1"/>
       <c r="AB183" s="1"/>
       <c r="AC183" s="1"/>
@@ -19314,7 +19337,7 @@
       <c r="W184" s="1"/>
       <c r="X184" s="1"/>
       <c r="Y184" s="1"/>
-      <c r="Z184" s="1"/>
+      <c r="Z184" s="23"/>
       <c r="AA184" s="1"/>
       <c r="AB184" s="1"/>
       <c r="AC184" s="1"/>
@@ -19366,7 +19389,7 @@
       <c r="W185" s="1"/>
       <c r="X185" s="1"/>
       <c r="Y185" s="1"/>
-      <c r="Z185" s="1"/>
+      <c r="Z185" s="23"/>
       <c r="AA185" s="1"/>
       <c r="AB185" s="1"/>
       <c r="AC185" s="1"/>
@@ -19418,7 +19441,7 @@
       <c r="W186" s="1"/>
       <c r="X186" s="1"/>
       <c r="Y186" s="1"/>
-      <c r="Z186" s="1"/>
+      <c r="Z186" s="23"/>
       <c r="AA186" s="1"/>
       <c r="AB186" s="1"/>
       <c r="AC186" s="1"/>
@@ -19470,7 +19493,7 @@
       <c r="W187" s="1"/>
       <c r="X187" s="1"/>
       <c r="Y187" s="1"/>
-      <c r="Z187" s="1"/>
+      <c r="Z187" s="23"/>
       <c r="AA187" s="1"/>
       <c r="AB187" s="1"/>
       <c r="AC187" s="1"/>
@@ -19522,7 +19545,7 @@
       <c r="W188" s="1"/>
       <c r="X188" s="1"/>
       <c r="Y188" s="1"/>
-      <c r="Z188" s="1"/>
+      <c r="Z188" s="23"/>
       <c r="AA188" s="1"/>
       <c r="AB188" s="1"/>
       <c r="AC188" s="1"/>
@@ -19574,7 +19597,7 @@
       <c r="W189" s="1"/>
       <c r="X189" s="1"/>
       <c r="Y189" s="1"/>
-      <c r="Z189" s="1"/>
+      <c r="Z189" s="23"/>
       <c r="AA189" s="1"/>
       <c r="AB189" s="1"/>
       <c r="AC189" s="1"/>
@@ -19626,7 +19649,7 @@
       <c r="W190" s="1"/>
       <c r="X190" s="1"/>
       <c r="Y190" s="1"/>
-      <c r="Z190" s="1"/>
+      <c r="Z190" s="23"/>
       <c r="AA190" s="1"/>
       <c r="AB190" s="1"/>
       <c r="AC190" s="1"/>
@@ -19678,7 +19701,7 @@
       <c r="W191" s="1"/>
       <c r="X191" s="1"/>
       <c r="Y191" s="1"/>
-      <c r="Z191" s="1"/>
+      <c r="Z191" s="23"/>
       <c r="AA191" s="1"/>
       <c r="AB191" s="1"/>
       <c r="AC191" s="1"/>
@@ -19730,7 +19753,7 @@
       <c r="W192" s="1"/>
       <c r="X192" s="1"/>
       <c r="Y192" s="1"/>
-      <c r="Z192" s="1"/>
+      <c r="Z192" s="23"/>
       <c r="AA192" s="1"/>
       <c r="AB192" s="1"/>
       <c r="AC192" s="1"/>
@@ -19782,7 +19805,7 @@
       <c r="W193" s="1"/>
       <c r="X193" s="1"/>
       <c r="Y193" s="1"/>
-      <c r="Z193" s="1"/>
+      <c r="Z193" s="23"/>
       <c r="AA193" s="1"/>
       <c r="AB193" s="1"/>
       <c r="AC193" s="1"/>
@@ -19834,7 +19857,7 @@
       <c r="W194" s="1"/>
       <c r="X194" s="1"/>
       <c r="Y194" s="1"/>
-      <c r="Z194" s="1"/>
+      <c r="Z194" s="23"/>
       <c r="AA194" s="1"/>
       <c r="AB194" s="1"/>
       <c r="AC194" s="1"/>
@@ -19886,7 +19909,7 @@
       <c r="W195" s="1"/>
       <c r="X195" s="1"/>
       <c r="Y195" s="1"/>
-      <c r="Z195" s="1"/>
+      <c r="Z195" s="23"/>
       <c r="AA195" s="1"/>
       <c r="AB195" s="1"/>
       <c r="AC195" s="1"/>
@@ -19938,7 +19961,7 @@
       <c r="W196" s="1"/>
       <c r="X196" s="1"/>
       <c r="Y196" s="1"/>
-      <c r="Z196" s="1"/>
+      <c r="Z196" s="23"/>
       <c r="AA196" s="1"/>
       <c r="AB196" s="1"/>
       <c r="AC196" s="1"/>
@@ -19990,7 +20013,7 @@
       <c r="W197" s="1"/>
       <c r="X197" s="1"/>
       <c r="Y197" s="1"/>
-      <c r="Z197" s="1"/>
+      <c r="Z197" s="23"/>
       <c r="AA197" s="1"/>
       <c r="AB197" s="1"/>
       <c r="AC197" s="1"/>
@@ -20042,7 +20065,7 @@
       <c r="W198" s="1"/>
       <c r="X198" s="1"/>
       <c r="Y198" s="1"/>
-      <c r="Z198" s="1"/>
+      <c r="Z198" s="23"/>
       <c r="AA198" s="1"/>
       <c r="AB198" s="1"/>
       <c r="AC198" s="1"/>
@@ -20094,7 +20117,7 @@
       <c r="W199" s="1"/>
       <c r="X199" s="1"/>
       <c r="Y199" s="1"/>
-      <c r="Z199" s="1"/>
+      <c r="Z199" s="23"/>
       <c r="AA199" s="1"/>
       <c r="AB199" s="1"/>
       <c r="AC199" s="1"/>
@@ -20146,7 +20169,7 @@
       <c r="W200" s="1"/>
       <c r="X200" s="1"/>
       <c r="Y200" s="1"/>
-      <c r="Z200" s="1"/>
+      <c r="Z200" s="23"/>
       <c r="AA200" s="1"/>
       <c r="AB200" s="1"/>
       <c r="AC200" s="1"/>
@@ -20198,7 +20221,7 @@
       <c r="W201" s="1"/>
       <c r="X201" s="1"/>
       <c r="Y201" s="1"/>
-      <c r="Z201" s="1"/>
+      <c r="Z201" s="23"/>
       <c r="AA201" s="1"/>
       <c r="AB201" s="1"/>
       <c r="AC201" s="1"/>
@@ -20250,7 +20273,7 @@
       <c r="W202" s="1"/>
       <c r="X202" s="1"/>
       <c r="Y202" s="1"/>
-      <c r="Z202" s="1"/>
+      <c r="Z202" s="23"/>
       <c r="AA202" s="1"/>
       <c r="AB202" s="1"/>
       <c r="AC202" s="1"/>
@@ -20302,7 +20325,7 @@
       <c r="W203" s="1"/>
       <c r="X203" s="1"/>
       <c r="Y203" s="1"/>
-      <c r="Z203" s="1"/>
+      <c r="Z203" s="23"/>
       <c r="AA203" s="1"/>
       <c r="AB203" s="1"/>
       <c r="AC203" s="1"/>
@@ -20354,7 +20377,7 @@
       <c r="W204" s="1"/>
       <c r="X204" s="1"/>
       <c r="Y204" s="1"/>
-      <c r="Z204" s="1"/>
+      <c r="Z204" s="23"/>
       <c r="AA204" s="1"/>
       <c r="AB204" s="1"/>
       <c r="AC204" s="1"/>
@@ -20406,7 +20429,7 @@
       <c r="W205" s="1"/>
       <c r="X205" s="1"/>
       <c r="Y205" s="1"/>
-      <c r="Z205" s="1"/>
+      <c r="Z205" s="23"/>
       <c r="AA205" s="1"/>
       <c r="AB205" s="1"/>
       <c r="AC205" s="1"/>
@@ -20458,7 +20481,7 @@
       <c r="W206" s="1"/>
       <c r="X206" s="1"/>
       <c r="Y206" s="1"/>
-      <c r="Z206" s="1"/>
+      <c r="Z206" s="23"/>
       <c r="AA206" s="1"/>
       <c r="AB206" s="1"/>
       <c r="AC206" s="1"/>
@@ -20510,7 +20533,7 @@
       <c r="W207" s="1"/>
       <c r="X207" s="1"/>
       <c r="Y207" s="1"/>
-      <c r="Z207" s="1"/>
+      <c r="Z207" s="23"/>
       <c r="AA207" s="1"/>
       <c r="AB207" s="1"/>
       <c r="AC207" s="1"/>
@@ -20562,7 +20585,7 @@
       <c r="W208" s="1"/>
       <c r="X208" s="1"/>
       <c r="Y208" s="1"/>
-      <c r="Z208" s="1"/>
+      <c r="Z208" s="23"/>
       <c r="AA208" s="1"/>
       <c r="AB208" s="1"/>
       <c r="AC208" s="1"/>
@@ -20614,7 +20637,7 @@
       <c r="W209" s="1"/>
       <c r="X209" s="1"/>
       <c r="Y209" s="1"/>
-      <c r="Z209" s="1"/>
+      <c r="Z209" s="23"/>
       <c r="AA209" s="1"/>
       <c r="AB209" s="1"/>
       <c r="AC209" s="1"/>
@@ -20666,7 +20689,7 @@
       <c r="W210" s="1"/>
       <c r="X210" s="1"/>
       <c r="Y210" s="1"/>
-      <c r="Z210" s="1"/>
+      <c r="Z210" s="23"/>
       <c r="AA210" s="1"/>
       <c r="AB210" s="1"/>
       <c r="AC210" s="1"/>
@@ -20718,7 +20741,7 @@
       <c r="W211" s="1"/>
       <c r="X211" s="1"/>
       <c r="Y211" s="1"/>
-      <c r="Z211" s="1"/>
+      <c r="Z211" s="23"/>
       <c r="AA211" s="1"/>
       <c r="AB211" s="1"/>
       <c r="AC211" s="1"/>
@@ -20770,7 +20793,7 @@
       <c r="W212" s="1"/>
       <c r="X212" s="1"/>
       <c r="Y212" s="1"/>
-      <c r="Z212" s="1"/>
+      <c r="Z212" s="23"/>
       <c r="AA212" s="1"/>
       <c r="AB212" s="1"/>
       <c r="AC212" s="1"/>
@@ -20822,7 +20845,7 @@
       <c r="W213" s="1"/>
       <c r="X213" s="1"/>
       <c r="Y213" s="1"/>
-      <c r="Z213" s="1"/>
+      <c r="Z213" s="23"/>
       <c r="AA213" s="1"/>
       <c r="AB213" s="1"/>
       <c r="AC213" s="1"/>
@@ -20874,7 +20897,7 @@
       <c r="W214" s="1"/>
       <c r="X214" s="1"/>
       <c r="Y214" s="1"/>
-      <c r="Z214" s="1"/>
+      <c r="Z214" s="23"/>
       <c r="AA214" s="1"/>
       <c r="AB214" s="1"/>
       <c r="AC214" s="1"/>
@@ -20926,7 +20949,7 @@
       <c r="W215" s="1"/>
       <c r="X215" s="1"/>
       <c r="Y215" s="1"/>
-      <c r="Z215" s="1"/>
+      <c r="Z215" s="23"/>
       <c r="AA215" s="1"/>
       <c r="AB215" s="1"/>
       <c r="AC215" s="1"/>
@@ -20978,7 +21001,7 @@
       <c r="W216" s="1"/>
       <c r="X216" s="1"/>
       <c r="Y216" s="1"/>
-      <c r="Z216" s="1"/>
+      <c r="Z216" s="23"/>
       <c r="AA216" s="1"/>
       <c r="AB216" s="1"/>
       <c r="AC216" s="1"/>
@@ -21030,7 +21053,7 @@
       <c r="W217" s="1"/>
       <c r="X217" s="1"/>
       <c r="Y217" s="1"/>
-      <c r="Z217" s="1"/>
+      <c r="Z217" s="23"/>
       <c r="AA217" s="1"/>
       <c r="AB217" s="1"/>
       <c r="AC217" s="1"/>
@@ -21082,7 +21105,7 @@
       <c r="W218" s="1"/>
       <c r="X218" s="1"/>
       <c r="Y218" s="1"/>
-      <c r="Z218" s="1"/>
+      <c r="Z218" s="23"/>
       <c r="AA218" s="1"/>
       <c r="AB218" s="1"/>
       <c r="AC218" s="1"/>
@@ -21134,7 +21157,7 @@
       <c r="W219" s="1"/>
       <c r="X219" s="1"/>
       <c r="Y219" s="1"/>
-      <c r="Z219" s="1"/>
+      <c r="Z219" s="23"/>
       <c r="AA219" s="1"/>
       <c r="AB219" s="1"/>
       <c r="AC219" s="1"/>
@@ -21186,7 +21209,7 @@
       <c r="W220" s="1"/>
       <c r="X220" s="1"/>
       <c r="Y220" s="1"/>
-      <c r="Z220" s="1"/>
+      <c r="Z220" s="23"/>
       <c r="AA220" s="1"/>
       <c r="AB220" s="1"/>
       <c r="AC220" s="1"/>
@@ -21238,7 +21261,7 @@
       <c r="W221" s="1"/>
       <c r="X221" s="1"/>
       <c r="Y221" s="1"/>
-      <c r="Z221" s="1"/>
+      <c r="Z221" s="23"/>
       <c r="AA221" s="1"/>
       <c r="AB221" s="1"/>
       <c r="AC221" s="1"/>
@@ -21290,7 +21313,7 @@
       <c r="W222" s="1"/>
       <c r="X222" s="1"/>
       <c r="Y222" s="1"/>
-      <c r="Z222" s="1"/>
+      <c r="Z222" s="23"/>
       <c r="AA222" s="1"/>
       <c r="AB222" s="1"/>
       <c r="AC222" s="1"/>
@@ -21342,7 +21365,7 @@
       <c r="W223" s="1"/>
       <c r="X223" s="1"/>
       <c r="Y223" s="1"/>
-      <c r="Z223" s="1"/>
+      <c r="Z223" s="23"/>
       <c r="AA223" s="1"/>
       <c r="AB223" s="1"/>
       <c r="AC223" s="1"/>
@@ -21394,7 +21417,7 @@
       <c r="W224" s="1"/>
       <c r="X224" s="1"/>
       <c r="Y224" s="1"/>
-      <c r="Z224" s="1"/>
+      <c r="Z224" s="23"/>
       <c r="AA224" s="1"/>
       <c r="AB224" s="1"/>
       <c r="AC224" s="1"/>
@@ -21446,7 +21469,7 @@
       <c r="W225" s="1"/>
       <c r="X225" s="1"/>
       <c r="Y225" s="1"/>
-      <c r="Z225" s="1"/>
+      <c r="Z225" s="23"/>
       <c r="AA225" s="1"/>
       <c r="AB225" s="1"/>
       <c r="AC225" s="1"/>
@@ -21498,7 +21521,7 @@
       <c r="W226" s="1"/>
       <c r="X226" s="1"/>
       <c r="Y226" s="1"/>
-      <c r="Z226" s="1"/>
+      <c r="Z226" s="23"/>
       <c r="AA226" s="1"/>
       <c r="AB226" s="1"/>
       <c r="AC226" s="1"/>
@@ -21550,7 +21573,7 @@
       <c r="W227" s="1"/>
       <c r="X227" s="1"/>
       <c r="Y227" s="1"/>
-      <c r="Z227" s="1"/>
+      <c r="Z227" s="23"/>
       <c r="AA227" s="1"/>
       <c r="AB227" s="1"/>
       <c r="AC227" s="1"/>
@@ -21602,7 +21625,7 @@
       <c r="W228" s="1"/>
       <c r="X228" s="1"/>
       <c r="Y228" s="1"/>
-      <c r="Z228" s="1"/>
+      <c r="Z228" s="23"/>
       <c r="AA228" s="1"/>
       <c r="AB228" s="1"/>
       <c r="AC228" s="1"/>
@@ -21654,7 +21677,7 @@
       <c r="W229" s="1"/>
       <c r="X229" s="1"/>
       <c r="Y229" s="1"/>
-      <c r="Z229" s="1"/>
+      <c r="Z229" s="23"/>
       <c r="AA229" s="1"/>
       <c r="AB229" s="1"/>
       <c r="AC229" s="1"/>
@@ -21706,7 +21729,7 @@
       <c r="W230" s="1"/>
       <c r="X230" s="1"/>
       <c r="Y230" s="1"/>
-      <c r="Z230" s="1"/>
+      <c r="Z230" s="23"/>
       <c r="AA230" s="1"/>
       <c r="AB230" s="1"/>
       <c r="AC230" s="1"/>
@@ -21758,7 +21781,7 @@
       <c r="W231" s="1"/>
       <c r="X231" s="1"/>
       <c r="Y231" s="1"/>
-      <c r="Z231" s="1"/>
+      <c r="Z231" s="23"/>
       <c r="AA231" s="1"/>
       <c r="AB231" s="1"/>
       <c r="AC231" s="1"/>
@@ -21810,7 +21833,7 @@
       <c r="W232" s="1"/>
       <c r="X232" s="1"/>
       <c r="Y232" s="1"/>
-      <c r="Z232" s="1"/>
+      <c r="Z232" s="23"/>
       <c r="AA232" s="1"/>
       <c r="AB232" s="1"/>
       <c r="AC232" s="1"/>
@@ -21862,7 +21885,7 @@
       <c r="W233" s="1"/>
       <c r="X233" s="1"/>
       <c r="Y233" s="1"/>
-      <c r="Z233" s="1"/>
+      <c r="Z233" s="23"/>
       <c r="AA233" s="1"/>
       <c r="AB233" s="1"/>
       <c r="AC233" s="1"/>
@@ -21914,7 +21937,7 @@
       <c r="W234" s="1"/>
       <c r="X234" s="1"/>
       <c r="Y234" s="1"/>
-      <c r="Z234" s="1"/>
+      <c r="Z234" s="23"/>
       <c r="AA234" s="1"/>
       <c r="AB234" s="1"/>
       <c r="AC234" s="1"/>
@@ -21966,7 +21989,7 @@
       <c r="W235" s="1"/>
       <c r="X235" s="1"/>
       <c r="Y235" s="1"/>
-      <c r="Z235" s="1"/>
+      <c r="Z235" s="23"/>
       <c r="AA235" s="1"/>
       <c r="AB235" s="1"/>
       <c r="AC235" s="1"/>
@@ -22018,7 +22041,7 @@
       <c r="W236" s="1"/>
       <c r="X236" s="1"/>
       <c r="Y236" s="1"/>
-      <c r="Z236" s="1"/>
+      <c r="Z236" s="23"/>
       <c r="AA236" s="1"/>
       <c r="AB236" s="1"/>
       <c r="AC236" s="1"/>
@@ -22070,7 +22093,7 @@
       <c r="W237" s="1"/>
       <c r="X237" s="1"/>
       <c r="Y237" s="1"/>
-      <c r="Z237" s="1"/>
+      <c r="Z237" s="23"/>
       <c r="AA237" s="1"/>
       <c r="AB237" s="1"/>
       <c r="AC237" s="1"/>
@@ -22122,7 +22145,7 @@
       <c r="W238" s="1"/>
       <c r="X238" s="1"/>
       <c r="Y238" s="1"/>
-      <c r="Z238" s="1"/>
+      <c r="Z238" s="23"/>
       <c r="AA238" s="1"/>
       <c r="AB238" s="1"/>
       <c r="AC238" s="1"/>
@@ -22174,7 +22197,7 @@
       <c r="W239" s="1"/>
       <c r="X239" s="1"/>
       <c r="Y239" s="1"/>
-      <c r="Z239" s="1"/>
+      <c r="Z239" s="23"/>
       <c r="AA239" s="1"/>
       <c r="AB239" s="1"/>
       <c r="AC239" s="1"/>
@@ -22226,7 +22249,7 @@
       <c r="W240" s="1"/>
       <c r="X240" s="1"/>
       <c r="Y240" s="1"/>
-      <c r="Z240" s="1"/>
+      <c r="Z240" s="23"/>
       <c r="AA240" s="1"/>
       <c r="AB240" s="1"/>
       <c r="AC240" s="1"/>
@@ -22278,7 +22301,7 @@
       <c r="W241" s="1"/>
       <c r="X241" s="1"/>
       <c r="Y241" s="1"/>
-      <c r="Z241" s="1"/>
+      <c r="Z241" s="23"/>
       <c r="AA241" s="1"/>
       <c r="AB241" s="1"/>
       <c r="AC241" s="1"/>
@@ -22330,7 +22353,7 @@
       <c r="W242" s="1"/>
       <c r="X242" s="1"/>
       <c r="Y242" s="1"/>
-      <c r="Z242" s="1"/>
+      <c r="Z242" s="23"/>
       <c r="AA242" s="1"/>
       <c r="AB242" s="1"/>
       <c r="AC242" s="1"/>
@@ -22382,7 +22405,7 @@
       <c r="W243" s="1"/>
       <c r="X243" s="1"/>
       <c r="Y243" s="1"/>
-      <c r="Z243" s="1"/>
+      <c r="Z243" s="23"/>
       <c r="AA243" s="1"/>
       <c r="AB243" s="1"/>
       <c r="AC243" s="1"/>
@@ -22434,7 +22457,7 @@
       <c r="W244" s="1"/>
       <c r="X244" s="1"/>
       <c r="Y244" s="1"/>
-      <c r="Z244" s="1"/>
+      <c r="Z244" s="23"/>
       <c r="AA244" s="1"/>
       <c r="AB244" s="1"/>
       <c r="AC244" s="1"/>
@@ -22486,7 +22509,7 @@
       <c r="W245" s="1"/>
       <c r="X245" s="1"/>
       <c r="Y245" s="1"/>
-      <c r="Z245" s="1"/>
+      <c r="Z245" s="23"/>
       <c r="AA245" s="1"/>
       <c r="AB245" s="1"/>
       <c r="AC245" s="1"/>
@@ -22538,7 +22561,7 @@
       <c r="W246" s="1"/>
       <c r="X246" s="1"/>
       <c r="Y246" s="1"/>
-      <c r="Z246" s="1"/>
+      <c r="Z246" s="23"/>
       <c r="AA246" s="1"/>
       <c r="AB246" s="1"/>
       <c r="AC246" s="1"/>
@@ -22590,7 +22613,7 @@
       <c r="W247" s="1"/>
       <c r="X247" s="1"/>
       <c r="Y247" s="1"/>
-      <c r="Z247" s="1"/>
+      <c r="Z247" s="23"/>
       <c r="AA247" s="1"/>
       <c r="AB247" s="1"/>
       <c r="AC247" s="1"/>
@@ -22642,7 +22665,7 @@
       <c r="W248" s="1"/>
       <c r="X248" s="1"/>
       <c r="Y248" s="1"/>
-      <c r="Z248" s="1"/>
+      <c r="Z248" s="23"/>
       <c r="AA248" s="1"/>
       <c r="AB248" s="1"/>
       <c r="AC248" s="1"/>
@@ -22694,7 +22717,7 @@
       <c r="W249" s="1"/>
       <c r="X249" s="1"/>
       <c r="Y249" s="1"/>
-      <c r="Z249" s="1"/>
+      <c r="Z249" s="23"/>
       <c r="AA249" s="1"/>
       <c r="AB249" s="1"/>
       <c r="AC249" s="1"/>
@@ -22746,7 +22769,7 @@
       <c r="W250" s="1"/>
       <c r="X250" s="1"/>
       <c r="Y250" s="1"/>
-      <c r="Z250" s="1"/>
+      <c r="Z250" s="23"/>
       <c r="AA250" s="1"/>
       <c r="AB250" s="1"/>
       <c r="AC250" s="1"/>
@@ -22798,7 +22821,7 @@
       <c r="W251" s="1"/>
       <c r="X251" s="1"/>
       <c r="Y251" s="1"/>
-      <c r="Z251" s="1"/>
+      <c r="Z251" s="23"/>
       <c r="AA251" s="1"/>
       <c r="AB251" s="1"/>
       <c r="AC251" s="1"/>
@@ -22850,7 +22873,7 @@
       <c r="W252" s="1"/>
       <c r="X252" s="1"/>
       <c r="Y252" s="1"/>
-      <c r="Z252" s="1"/>
+      <c r="Z252" s="23"/>
       <c r="AA252" s="1"/>
       <c r="AB252" s="1"/>
       <c r="AC252" s="1"/>
@@ -22902,7 +22925,7 @@
       <c r="W253" s="1"/>
       <c r="X253" s="1"/>
       <c r="Y253" s="1"/>
-      <c r="Z253" s="1"/>
+      <c r="Z253" s="23"/>
       <c r="AA253" s="1"/>
       <c r="AB253" s="1"/>
       <c r="AC253" s="1"/>
@@ -22954,7 +22977,7 @@
       <c r="W254" s="1"/>
       <c r="X254" s="1"/>
       <c r="Y254" s="1"/>
-      <c r="Z254" s="1"/>
+      <c r="Z254" s="23"/>
       <c r="AA254" s="1"/>
       <c r="AB254" s="1"/>
       <c r="AC254" s="1"/>
@@ -23006,7 +23029,7 @@
       <c r="W255" s="1"/>
       <c r="X255" s="1"/>
       <c r="Y255" s="1"/>
-      <c r="Z255" s="1"/>
+      <c r="Z255" s="23"/>
       <c r="AA255" s="1"/>
       <c r="AB255" s="1"/>
       <c r="AC255" s="1"/>
@@ -23058,7 +23081,7 @@
       <c r="W256" s="1"/>
       <c r="X256" s="1"/>
       <c r="Y256" s="1"/>
-      <c r="Z256" s="1"/>
+      <c r="Z256" s="23"/>
       <c r="AA256" s="1"/>
       <c r="AB256" s="1"/>
       <c r="AC256" s="1"/>
@@ -23110,7 +23133,7 @@
       <c r="W257" s="1"/>
       <c r="X257" s="1"/>
       <c r="Y257" s="1"/>
-      <c r="Z257" s="1"/>
+      <c r="Z257" s="23"/>
       <c r="AA257" s="1"/>
       <c r="AB257" s="1"/>
       <c r="AC257" s="1"/>
@@ -23162,7 +23185,7 @@
       <c r="W258" s="1"/>
       <c r="X258" s="1"/>
       <c r="Y258" s="1"/>
-      <c r="Z258" s="1"/>
+      <c r="Z258" s="23"/>
       <c r="AA258" s="1"/>
       <c r="AB258" s="1"/>
       <c r="AC258" s="1"/>
@@ -23214,7 +23237,7 @@
       <c r="W259" s="1"/>
       <c r="X259" s="1"/>
       <c r="Y259" s="1"/>
-      <c r="Z259" s="1"/>
+      <c r="Z259" s="23"/>
       <c r="AA259" s="1"/>
       <c r="AB259" s="1"/>
       <c r="AC259" s="1"/>
@@ -23266,7 +23289,7 @@
       <c r="W260" s="1"/>
       <c r="X260" s="1"/>
       <c r="Y260" s="1"/>
-      <c r="Z260" s="1"/>
+      <c r="Z260" s="23"/>
       <c r="AA260" s="1"/>
       <c r="AB260" s="1"/>
       <c r="AC260" s="1"/>
@@ -23318,7 +23341,7 @@
       <c r="W261" s="1"/>
       <c r="X261" s="1"/>
       <c r="Y261" s="1"/>
-      <c r="Z261" s="1"/>
+      <c r="Z261" s="23"/>
       <c r="AA261" s="1"/>
       <c r="AB261" s="1"/>
       <c r="AC261" s="1"/>
@@ -23370,7 +23393,7 @@
       <c r="W262" s="1"/>
       <c r="X262" s="1"/>
       <c r="Y262" s="1"/>
-      <c r="Z262" s="1"/>
+      <c r="Z262" s="23"/>
       <c r="AA262" s="1"/>
       <c r="AB262" s="1"/>
       <c r="AC262" s="1"/>
@@ -23422,7 +23445,7 @@
       <c r="W263" s="1"/>
       <c r="X263" s="1"/>
       <c r="Y263" s="1"/>
-      <c r="Z263" s="1"/>
+      <c r="Z263" s="23"/>
       <c r="AA263" s="1"/>
       <c r="AB263" s="1"/>
       <c r="AC263" s="1"/>
@@ -23474,7 +23497,7 @@
       <c r="W264" s="1"/>
       <c r="X264" s="1"/>
       <c r="Y264" s="1"/>
-      <c r="Z264" s="1"/>
+      <c r="Z264" s="23"/>
       <c r="AA264" s="1"/>
       <c r="AB264" s="1"/>
       <c r="AC264" s="1"/>
@@ -23526,7 +23549,7 @@
       <c r="W265" s="1"/>
       <c r="X265" s="1"/>
       <c r="Y265" s="1"/>
-      <c r="Z265" s="1"/>
+      <c r="Z265" s="23"/>
       <c r="AA265" s="1"/>
       <c r="AB265" s="1"/>
       <c r="AC265" s="1"/>
@@ -23578,7 +23601,7 @@
       <c r="W266" s="1"/>
       <c r="X266" s="1"/>
       <c r="Y266" s="1"/>
-      <c r="Z266" s="1"/>
+      <c r="Z266" s="23"/>
       <c r="AA266" s="1"/>
       <c r="AB266" s="1"/>
       <c r="AC266" s="1"/>
@@ -23630,7 +23653,7 @@
       <c r="W267" s="1"/>
       <c r="X267" s="1"/>
       <c r="Y267" s="1"/>
-      <c r="Z267" s="1"/>
+      <c r="Z267" s="23"/>
       <c r="AA267" s="1"/>
       <c r="AB267" s="1"/>
       <c r="AC267" s="1"/>
@@ -23682,7 +23705,7 @@
       <c r="W268" s="1"/>
       <c r="X268" s="1"/>
       <c r="Y268" s="1"/>
-      <c r="Z268" s="1"/>
+      <c r="Z268" s="23"/>
       <c r="AA268" s="1"/>
       <c r="AB268" s="1"/>
       <c r="AC268" s="1"/>
@@ -23734,7 +23757,7 @@
       <c r="W269" s="1"/>
       <c r="X269" s="1"/>
       <c r="Y269" s="1"/>
-      <c r="Z269" s="1"/>
+      <c r="Z269" s="23"/>
       <c r="AA269" s="1"/>
       <c r="AB269" s="1"/>
       <c r="AC269" s="1"/>
@@ -23786,7 +23809,7 @@
       <c r="W270" s="1"/>
       <c r="X270" s="1"/>
       <c r="Y270" s="1"/>
-      <c r="Z270" s="1"/>
+      <c r="Z270" s="23"/>
       <c r="AA270" s="1"/>
       <c r="AB270" s="1"/>
       <c r="AC270" s="1"/>
@@ -23838,7 +23861,7 @@
       <c r="W271" s="1"/>
       <c r="X271" s="1"/>
       <c r="Y271" s="1"/>
-      <c r="Z271" s="1"/>
+      <c r="Z271" s="23"/>
       <c r="AA271" s="1"/>
       <c r="AB271" s="1"/>
       <c r="AC271" s="1"/>
@@ -23890,7 +23913,7 @@
       <c r="W272" s="1"/>
       <c r="X272" s="1"/>
       <c r="Y272" s="1"/>
-      <c r="Z272" s="1"/>
+      <c r="Z272" s="23"/>
       <c r="AA272" s="1"/>
       <c r="AB272" s="1"/>
       <c r="AC272" s="1"/>
@@ -23942,7 +23965,7 @@
       <c r="W273" s="1"/>
       <c r="X273" s="1"/>
       <c r="Y273" s="1"/>
-      <c r="Z273" s="1"/>
+      <c r="Z273" s="23"/>
       <c r="AA273" s="1"/>
       <c r="AB273" s="1"/>
       <c r="AC273" s="1"/>
@@ -23994,7 +24017,7 @@
       <c r="W274" s="1"/>
       <c r="X274" s="1"/>
       <c r="Y274" s="1"/>
-      <c r="Z274" s="1"/>
+      <c r="Z274" s="23"/>
       <c r="AA274" s="1"/>
       <c r="AB274" s="1"/>
       <c r="AC274" s="1"/>
@@ -24046,7 +24069,7 @@
       <c r="W275" s="1"/>
       <c r="X275" s="1"/>
       <c r="Y275" s="1"/>
-      <c r="Z275" s="1"/>
+      <c r="Z275" s="23"/>
       <c r="AA275" s="1"/>
       <c r="AB275" s="1"/>
       <c r="AC275" s="1"/>
@@ -24098,7 +24121,7 @@
       <c r="W276" s="1"/>
       <c r="X276" s="1"/>
       <c r="Y276" s="1"/>
-      <c r="Z276" s="1"/>
+      <c r="Z276" s="23"/>
       <c r="AA276" s="1"/>
       <c r="AB276" s="1"/>
       <c r="AC276" s="1"/>
@@ -24150,7 +24173,7 @@
       <c r="W277" s="1"/>
       <c r="X277" s="1"/>
       <c r="Y277" s="1"/>
-      <c r="Z277" s="1"/>
+      <c r="Z277" s="23"/>
       <c r="AA277" s="1"/>
       <c r="AB277" s="1"/>
       <c r="AC277" s="1"/>
@@ -24202,7 +24225,7 @@
       <c r="W278" s="1"/>
       <c r="X278" s="1"/>
       <c r="Y278" s="1"/>
-      <c r="Z278" s="1"/>
+      <c r="Z278" s="23"/>
       <c r="AA278" s="1"/>
       <c r="AB278" s="1"/>
       <c r="AC278" s="1"/>
@@ -24254,7 +24277,7 @@
       <c r="W279" s="1"/>
       <c r="X279" s="1"/>
       <c r="Y279" s="1"/>
-      <c r="Z279" s="1"/>
+      <c r="Z279" s="23"/>
       <c r="AA279" s="1"/>
       <c r="AB279" s="1"/>
       <c r="AC279" s="1"/>
@@ -24306,7 +24329,7 @@
       <c r="W280" s="1"/>
       <c r="X280" s="1"/>
       <c r="Y280" s="1"/>
-      <c r="Z280" s="1"/>
+      <c r="Z280" s="23"/>
       <c r="AA280" s="1"/>
       <c r="AB280" s="1"/>
       <c r="AC280" s="1"/>
@@ -24358,7 +24381,7 @@
       <c r="W281" s="1"/>
       <c r="X281" s="1"/>
       <c r="Y281" s="1"/>
-      <c r="Z281" s="1"/>
+      <c r="Z281" s="23"/>
       <c r="AA281" s="1"/>
       <c r="AB281" s="1"/>
       <c r="AC281" s="1"/>
@@ -24410,7 +24433,7 @@
       <c r="W282" s="1"/>
       <c r="X282" s="1"/>
       <c r="Y282" s="1"/>
-      <c r="Z282" s="1"/>
+      <c r="Z282" s="23"/>
       <c r="AA282" s="1"/>
       <c r="AB282" s="1"/>
       <c r="AC282" s="1"/>
@@ -24462,7 +24485,7 @@
       <c r="W283" s="1"/>
       <c r="X283" s="1"/>
       <c r="Y283" s="1"/>
-      <c r="Z283" s="1"/>
+      <c r="Z283" s="23"/>
       <c r="AA283" s="1"/>
       <c r="AB283" s="1"/>
       <c r="AC283" s="1"/>
@@ -24514,7 +24537,7 @@
       <c r="W284" s="1"/>
       <c r="X284" s="1"/>
       <c r="Y284" s="1"/>
-      <c r="Z284" s="1"/>
+      <c r="Z284" s="23"/>
       <c r="AA284" s="1"/>
       <c r="AB284" s="1"/>
       <c r="AC284" s="1"/>
@@ -24566,7 +24589,7 @@
       <c r="W285" s="1"/>
       <c r="X285" s="1"/>
       <c r="Y285" s="1"/>
-      <c r="Z285" s="1"/>
+      <c r="Z285" s="23"/>
       <c r="AA285" s="1"/>
       <c r="AB285" s="1"/>
       <c r="AC285" s="1"/>
@@ -24618,7 +24641,7 @@
       <c r="W286" s="1"/>
       <c r="X286" s="1"/>
       <c r="Y286" s="1"/>
-      <c r="Z286" s="1"/>
+      <c r="Z286" s="23"/>
       <c r="AA286" s="1"/>
       <c r="AB286" s="1"/>
       <c r="AC286" s="1"/>
@@ -24670,7 +24693,7 @@
       <c r="W287" s="1"/>
       <c r="X287" s="1"/>
       <c r="Y287" s="1"/>
-      <c r="Z287" s="1"/>
+      <c r="Z287" s="23"/>
       <c r="AA287" s="1"/>
       <c r="AB287" s="1"/>
       <c r="AC287" s="1"/>
@@ -24722,7 +24745,7 @@
       <c r="W288" s="1"/>
       <c r="X288" s="1"/>
       <c r="Y288" s="1"/>
-      <c r="Z288" s="1"/>
+      <c r="Z288" s="23"/>
       <c r="AA288" s="1"/>
       <c r="AB288" s="1"/>
       <c r="AC288" s="1"/>
@@ -24774,7 +24797,7 @@
       <c r="W289" s="1"/>
       <c r="X289" s="1"/>
       <c r="Y289" s="1"/>
-      <c r="Z289" s="1"/>
+      <c r="Z289" s="23"/>
       <c r="AA289" s="1"/>
       <c r="AB289" s="1"/>
       <c r="AC289" s="1"/>
@@ -24826,7 +24849,7 @@
       <c r="W290" s="1"/>
       <c r="X290" s="1"/>
       <c r="Y290" s="1"/>
-      <c r="Z290" s="1"/>
+      <c r="Z290" s="23"/>
       <c r="AA290" s="1"/>
       <c r="AB290" s="1"/>
       <c r="AC290" s="1"/>
@@ -24878,7 +24901,7 @@
       <c r="W291" s="1"/>
       <c r="X291" s="1"/>
       <c r="Y291" s="1"/>
-      <c r="Z291" s="1"/>
+      <c r="Z291" s="23"/>
       <c r="AA291" s="1"/>
       <c r="AB291" s="1"/>
       <c r="AC291" s="1"/>
@@ -24930,7 +24953,7 @@
       <c r="W292" s="1"/>
       <c r="X292" s="1"/>
       <c r="Y292" s="1"/>
-      <c r="Z292" s="1"/>
+      <c r="Z292" s="23"/>
       <c r="AA292" s="1"/>
       <c r="AB292" s="1"/>
       <c r="AC292" s="1"/>
@@ -24982,7 +25005,7 @@
       <c r="W293" s="1"/>
       <c r="X293" s="1"/>
       <c r="Y293" s="1"/>
-      <c r="Z293" s="1"/>
+      <c r="Z293" s="23"/>
       <c r="AA293" s="1"/>
       <c r="AB293" s="1"/>
       <c r="AC293" s="1"/>
@@ -25034,7 +25057,7 @@
       <c r="W294" s="1"/>
       <c r="X294" s="1"/>
       <c r="Y294" s="1"/>
-      <c r="Z294" s="1"/>
+      <c r="Z294" s="23"/>
       <c r="AA294" s="1"/>
       <c r="AB294" s="1"/>
       <c r="AC294" s="1"/>
@@ -25086,7 +25109,7 @@
       <c r="W295" s="1"/>
       <c r="X295" s="1"/>
       <c r="Y295" s="1"/>
-      <c r="Z295" s="1"/>
+      <c r="Z295" s="23"/>
       <c r="AA295" s="1"/>
       <c r="AB295" s="1"/>
       <c r="AC295" s="1"/>
@@ -25138,7 +25161,7 @@
       <c r="W296" s="1"/>
       <c r="X296" s="1"/>
       <c r="Y296" s="1"/>
-      <c r="Z296" s="1"/>
+      <c r="Z296" s="23"/>
       <c r="AA296" s="1"/>
       <c r="AB296" s="1"/>
       <c r="AC296" s="1"/>
@@ -25190,7 +25213,7 @@
       <c r="W297" s="1"/>
       <c r="X297" s="1"/>
       <c r="Y297" s="1"/>
-      <c r="Z297" s="1"/>
+      <c r="Z297" s="23"/>
       <c r="AA297" s="1"/>
       <c r="AB297" s="1"/>
       <c r="AC297" s="1"/>
@@ -25242,7 +25265,7 @@
       <c r="W298" s="1"/>
       <c r="X298" s="1"/>
       <c r="Y298" s="1"/>
-      <c r="Z298" s="1"/>
+      <c r="Z298" s="23"/>
       <c r="AA298" s="1"/>
       <c r="AB298" s="1"/>
       <c r="AC298" s="1"/>
@@ -25294,7 +25317,7 @@
       <c r="W299" s="1"/>
       <c r="X299" s="1"/>
       <c r="Y299" s="1"/>
-      <c r="Z299" s="1"/>
+      <c r="Z299" s="23"/>
       <c r="AA299" s="1"/>
       <c r="AB299" s="1"/>
       <c r="AC299" s="1"/>
@@ -25346,7 +25369,7 @@
       <c r="W300" s="1"/>
       <c r="X300" s="1"/>
       <c r="Y300" s="1"/>
-      <c r="Z300" s="1"/>
+      <c r="Z300" s="23"/>
       <c r="AA300" s="1"/>
       <c r="AB300" s="1"/>
       <c r="AC300" s="1"/>
@@ -25398,7 +25421,7 @@
       <c r="W301" s="1"/>
       <c r="X301" s="1"/>
       <c r="Y301" s="1"/>
-      <c r="Z301" s="1"/>
+      <c r="Z301" s="23"/>
       <c r="AA301" s="1"/>
       <c r="AB301" s="1"/>
       <c r="AC301" s="1"/>
@@ -25450,7 +25473,7 @@
       <c r="W302" s="1"/>
       <c r="X302" s="1"/>
       <c r="Y302" s="1"/>
-      <c r="Z302" s="1"/>
+      <c r="Z302" s="23"/>
       <c r="AA302" s="1"/>
       <c r="AB302" s="1"/>
       <c r="AC302" s="1"/>
@@ -25502,7 +25525,7 @@
       <c r="W303" s="1"/>
       <c r="X303" s="1"/>
       <c r="Y303" s="1"/>
-      <c r="Z303" s="1"/>
+      <c r="Z303" s="23"/>
       <c r="AA303" s="1"/>
       <c r="AB303" s="1"/>
       <c r="AC303" s="1"/>
@@ -25554,7 +25577,7 @@
       <c r="W304" s="1"/>
       <c r="X304" s="1"/>
       <c r="Y304" s="1"/>
-      <c r="Z304" s="1"/>
+      <c r="Z304" s="23"/>
       <c r="AA304" s="1"/>
       <c r="AB304" s="1"/>
       <c r="AC304" s="1"/>
@@ -25606,7 +25629,7 @@
       <c r="W305" s="1"/>
       <c r="X305" s="1"/>
       <c r="Y305" s="1"/>
-      <c r="Z305" s="1"/>
+      <c r="Z305" s="23"/>
       <c r="AA305" s="1"/>
       <c r="AB305" s="1"/>
       <c r="AC305" s="1"/>
@@ -25658,7 +25681,7 @@
       <c r="W306" s="1"/>
       <c r="X306" s="1"/>
       <c r="Y306" s="1"/>
-      <c r="Z306" s="1"/>
+      <c r="Z306" s="23"/>
       <c r="AA306" s="1"/>
       <c r="AB306" s="1"/>
       <c r="AC306" s="1"/>
@@ -25710,7 +25733,7 @@
       <c r="W307" s="1"/>
       <c r="X307" s="1"/>
       <c r="Y307" s="1"/>
-      <c r="Z307" s="1"/>
+      <c r="Z307" s="23"/>
       <c r="AA307" s="1"/>
       <c r="AB307" s="1"/>
       <c r="AC307" s="1"/>
@@ -25762,7 +25785,7 @@
       <c r="W308" s="1"/>
       <c r="X308" s="1"/>
       <c r="Y308" s="1"/>
-      <c r="Z308" s="1"/>
+      <c r="Z308" s="23"/>
       <c r="AA308" s="1"/>
       <c r="AB308" s="1"/>
       <c r="AC308" s="1"/>
@@ -25814,7 +25837,7 @@
       <c r="W309" s="1"/>
       <c r="X309" s="1"/>
       <c r="Y309" s="1"/>
-      <c r="Z309" s="1"/>
+      <c r="Z309" s="23"/>
       <c r="AA309" s="1"/>
       <c r="AB309" s="1"/>
       <c r="AC309" s="1"/>
@@ -25866,7 +25889,7 @@
       <c r="W310" s="1"/>
       <c r="X310" s="1"/>
       <c r="Y310" s="1"/>
-      <c r="Z310" s="1"/>
+      <c r="Z310" s="23"/>
       <c r="AA310" s="1"/>
       <c r="AB310" s="1"/>
       <c r="AC310" s="1"/>
@@ -25918,7 +25941,7 @@
       <c r="W311" s="1"/>
       <c r="X311" s="1"/>
       <c r="Y311" s="1"/>
-      <c r="Z311" s="1"/>
+      <c r="Z311" s="23"/>
       <c r="AA311" s="1"/>
       <c r="AB311" s="1"/>
       <c r="AC311" s="1"/>
@@ -25970,7 +25993,7 @@
       <c r="W312" s="1"/>
       <c r="X312" s="1"/>
       <c r="Y312" s="1"/>
-      <c r="Z312" s="1"/>
+      <c r="Z312" s="23"/>
       <c r="AA312" s="1"/>
       <c r="AB312" s="1"/>
       <c r="AC312" s="1"/>
@@ -26022,7 +26045,7 @@
       <c r="W313" s="1"/>
       <c r="X313" s="1"/>
       <c r="Y313" s="1"/>
-      <c r="Z313" s="1"/>
+      <c r="Z313" s="23"/>
       <c r="AA313" s="1"/>
       <c r="AB313" s="1"/>
       <c r="AC313" s="1"/>
@@ -26074,7 +26097,7 @@
       <c r="W314" s="1"/>
       <c r="X314" s="1"/>
       <c r="Y314" s="1"/>
-      <c r="Z314" s="1"/>
+      <c r="Z314" s="23"/>
       <c r="AA314" s="1"/>
       <c r="AB314" s="1"/>
       <c r="AC314" s="1"/>
@@ -26126,7 +26149,7 @@
       <c r="W315" s="1"/>
       <c r="X315" s="1"/>
       <c r="Y315" s="1"/>
-      <c r="Z315" s="1"/>
+      <c r="Z315" s="23"/>
       <c r="AA315" s="1"/>
       <c r="AB315" s="1"/>
       <c r="AC315" s="1"/>
@@ -26178,7 +26201,7 @@
       <c r="W316" s="1"/>
       <c r="X316" s="1"/>
       <c r="Y316" s="1"/>
-      <c r="Z316" s="1"/>
+      <c r="Z316" s="23"/>
       <c r="AA316" s="1"/>
       <c r="AB316" s="1"/>
       <c r="AC316" s="1"/>
@@ -26230,7 +26253,7 @@
       <c r="W317" s="1"/>
       <c r="X317" s="1"/>
       <c r="Y317" s="1"/>
-      <c r="Z317" s="1"/>
+      <c r="Z317" s="23"/>
       <c r="AA317" s="1"/>
       <c r="AB317" s="1"/>
       <c r="AC317" s="1"/>
@@ -26282,7 +26305,7 @@
       <c r="W318" s="1"/>
       <c r="X318" s="1"/>
       <c r="Y318" s="1"/>
-      <c r="Z318" s="1"/>
+      <c r="Z318" s="23"/>
       <c r="AA318" s="1"/>
       <c r="AB318" s="1"/>
       <c r="AC318" s="1"/>
@@ -26334,7 +26357,7 @@
       <c r="W319" s="1"/>
       <c r="X319" s="1"/>
       <c r="Y319" s="1"/>
-      <c r="Z319" s="1"/>
+      <c r="Z319" s="23"/>
       <c r="AA319" s="1"/>
       <c r="AB319" s="1"/>
       <c r="AC319" s="1"/>
@@ -26386,7 +26409,7 @@
       <c r="W320" s="1"/>
       <c r="X320" s="1"/>
       <c r="Y320" s="1"/>
-      <c r="Z320" s="1"/>
+      <c r="Z320" s="23"/>
       <c r="AA320" s="1"/>
       <c r="AB320" s="1"/>
       <c r="AC320" s="1"/>
@@ -26438,7 +26461,7 @@
       <c r="W321" s="1"/>
       <c r="X321" s="1"/>
       <c r="Y321" s="1"/>
-      <c r="Z321" s="1"/>
+      <c r="Z321" s="23"/>
       <c r="AA321" s="1"/>
       <c r="AB321" s="1"/>
       <c r="AC321" s="1"/>
@@ -26490,7 +26513,7 @@
       <c r="W322" s="1"/>
       <c r="X322" s="1"/>
       <c r="Y322" s="1"/>
-      <c r="Z322" s="1"/>
+      <c r="Z322" s="23"/>
       <c r="AA322" s="1"/>
       <c r="AB322" s="1"/>
       <c r="AC322" s="1"/>
@@ -26542,7 +26565,7 @@
       <c r="W323" s="1"/>
       <c r="X323" s="1"/>
       <c r="Y323" s="1"/>
-      <c r="Z323" s="1"/>
+      <c r="Z323" s="23"/>
       <c r="AA323" s="1"/>
       <c r="AB323" s="1"/>
       <c r="AC323" s="1"/>
@@ -26594,7 +26617,7 @@
       <c r="W324" s="1"/>
       <c r="X324" s="1"/>
       <c r="Y324" s="1"/>
-      <c r="Z324" s="1"/>
+      <c r="Z324" s="23"/>
       <c r="AA324" s="1"/>
       <c r="AB324" s="1"/>
       <c r="AC324" s="1"/>
@@ -26646,7 +26669,7 @@
       <c r="W325" s="1"/>
       <c r="X325" s="1"/>
       <c r="Y325" s="1"/>
-      <c r="Z325" s="1"/>
+      <c r="Z325" s="23"/>
       <c r="AA325" s="1"/>
       <c r="AB325" s="1"/>
       <c r="AC325" s="1"/>
@@ -26698,7 +26721,7 @@
       <c r="W326" s="1"/>
       <c r="X326" s="1"/>
       <c r="Y326" s="1"/>
-      <c r="Z326" s="1"/>
+      <c r="Z326" s="23"/>
       <c r="AA326" s="1"/>
       <c r="AB326" s="1"/>
       <c r="AC326" s="1"/>
@@ -26750,7 +26773,7 @@
       <c r="W327" s="1"/>
       <c r="X327" s="1"/>
       <c r="Y327" s="1"/>
-      <c r="Z327" s="1"/>
+      <c r="Z327" s="23"/>
       <c r="AA327" s="1"/>
       <c r="AB327" s="1"/>
       <c r="AC327" s="1"/>
@@ -26802,7 +26825,7 @@
       <c r="W328" s="1"/>
       <c r="X328" s="1"/>
       <c r="Y328" s="1"/>
-      <c r="Z328" s="1"/>
+      <c r="Z328" s="23"/>
       <c r="AA328" s="1"/>
       <c r="AB328" s="1"/>
       <c r="AC328" s="1"/>
@@ -26854,7 +26877,7 @@
       <c r="W329" s="1"/>
       <c r="X329" s="1"/>
       <c r="Y329" s="1"/>
-      <c r="Z329" s="1"/>
+      <c r="Z329" s="23"/>
       <c r="AA329" s="1"/>
       <c r="AB329" s="1"/>
       <c r="AC329" s="1"/>
@@ -26906,7 +26929,7 @@
       <c r="W330" s="1"/>
       <c r="X330" s="1"/>
       <c r="Y330" s="1"/>
-      <c r="Z330" s="1"/>
+      <c r="Z330" s="23"/>
       <c r="AA330" s="1"/>
       <c r="AB330" s="1"/>
       <c r="AC330" s="1"/>
@@ -26958,7 +26981,7 @@
       <c r="W331" s="1"/>
       <c r="X331" s="1"/>
       <c r="Y331" s="1"/>
-      <c r="Z331" s="1"/>
+      <c r="Z331" s="23"/>
       <c r="AA331" s="1"/>
       <c r="AB331" s="1"/>
       <c r="AC331" s="1"/>
@@ -27010,7 +27033,7 @@
       <c r="W332" s="1"/>
       <c r="X332" s="1"/>
       <c r="Y332" s="1"/>
-      <c r="Z332" s="1"/>
+      <c r="Z332" s="23"/>
       <c r="AA332" s="1"/>
       <c r="AB332" s="1"/>
       <c r="AC332" s="1"/>
@@ -27062,7 +27085,7 @@
       <c r="W333" s="1"/>
       <c r="X333" s="1"/>
       <c r="Y333" s="1"/>
-      <c r="Z333" s="1"/>
+      <c r="Z333" s="23"/>
       <c r="AA333" s="1"/>
       <c r="AB333" s="1"/>
       <c r="AC333" s="1"/>
@@ -27114,7 +27137,7 @@
       <c r="W334" s="1"/>
       <c r="X334" s="1"/>
       <c r="Y334" s="1"/>
-      <c r="Z334" s="1"/>
+      <c r="Z334" s="23"/>
       <c r="AA334" s="1"/>
       <c r="AB334" s="1"/>
       <c r="AC334" s="1"/>
@@ -27166,7 +27189,7 @@
       <c r="W335" s="1"/>
       <c r="X335" s="1"/>
       <c r="Y335" s="1"/>
-      <c r="Z335" s="1"/>
+      <c r="Z335" s="23"/>
       <c r="AA335" s="1"/>
       <c r="AB335" s="1"/>
       <c r="AC335" s="1"/>
@@ -27218,7 +27241,7 @@
       <c r="W336" s="1"/>
       <c r="X336" s="1"/>
       <c r="Y336" s="1"/>
-      <c r="Z336" s="1"/>
+      <c r="Z336" s="23"/>
       <c r="AA336" s="1"/>
       <c r="AB336" s="1"/>
       <c r="AC336" s="1"/>
@@ -27270,7 +27293,7 @@
       <c r="W337" s="1"/>
       <c r="X337" s="1"/>
       <c r="Y337" s="1"/>
-      <c r="Z337" s="1"/>
+      <c r="Z337" s="23"/>
       <c r="AA337" s="1"/>
       <c r="AB337" s="1"/>
       <c r="AC337" s="1"/>
@@ -27322,7 +27345,7 @@
       <c r="W338" s="1"/>
       <c r="X338" s="1"/>
       <c r="Y338" s="1"/>
-      <c r="Z338" s="1"/>
+      <c r="Z338" s="23"/>
       <c r="AA338" s="1"/>
       <c r="AB338" s="1"/>
       <c r="AC338" s="1"/>
@@ -27374,7 +27397,7 @@
       <c r="W339" s="1"/>
       <c r="X339" s="1"/>
       <c r="Y339" s="1"/>
-      <c r="Z339" s="1"/>
+      <c r="Z339" s="23"/>
       <c r="AA339" s="1"/>
       <c r="AB339" s="1"/>
       <c r="AC339" s="1"/>
@@ -27426,7 +27449,7 @@
       <c r="W340" s="1"/>
       <c r="X340" s="1"/>
       <c r="Y340" s="1"/>
-      <c r="Z340" s="1"/>
+      <c r="Z340" s="23"/>
       <c r="AA340" s="1"/>
       <c r="AB340" s="1"/>
       <c r="AC340" s="1"/>
@@ -27478,7 +27501,7 @@
       <c r="W341" s="1"/>
       <c r="X341" s="1"/>
       <c r="Y341" s="1"/>
-      <c r="Z341" s="1"/>
+      <c r="Z341" s="23"/>
       <c r="AA341" s="1"/>
       <c r="AB341" s="1"/>
       <c r="AC341" s="1"/>
@@ -27530,7 +27553,7 @@
       <c r="W342" s="1"/>
       <c r="X342" s="1"/>
       <c r="Y342" s="1"/>
-      <c r="Z342" s="1"/>
+      <c r="Z342" s="23"/>
       <c r="AA342" s="1"/>
       <c r="AB342" s="1"/>
       <c r="AC342" s="1"/>
@@ -27582,7 +27605,7 @@
       <c r="W343" s="1"/>
       <c r="X343" s="1"/>
       <c r="Y343" s="1"/>
-      <c r="Z343" s="1"/>
+      <c r="Z343" s="23"/>
       <c r="AA343" s="1"/>
       <c r="AB343" s="1"/>
       <c r="AC343" s="1"/>
@@ -27634,7 +27657,7 @@
       <c r="W344" s="1"/>
       <c r="X344" s="1"/>
       <c r="Y344" s="1"/>
-      <c r="Z344" s="1"/>
+      <c r="Z344" s="23"/>
       <c r="AA344" s="1"/>
       <c r="AB344" s="1"/>
       <c r="AC344" s="1"/>
@@ -27686,7 +27709,7 @@
       <c r="W345" s="1"/>
       <c r="X345" s="1"/>
       <c r="Y345" s="1"/>
-      <c r="Z345" s="1"/>
+      <c r="Z345" s="23"/>
       <c r="AA345" s="1"/>
       <c r="AB345" s="1"/>
       <c r="AC345" s="1"/>
@@ -27738,7 +27761,7 @@
       <c r="W346" s="1"/>
       <c r="X346" s="1"/>
       <c r="Y346" s="1"/>
-      <c r="Z346" s="1"/>
+      <c r="Z346" s="23"/>
       <c r="AA346" s="1"/>
       <c r="AB346" s="1"/>
       <c r="AC346" s="1"/>
@@ -27790,7 +27813,7 @@
       <c r="W347" s="1"/>
       <c r="X347" s="1"/>
       <c r="Y347" s="1"/>
-      <c r="Z347" s="1"/>
+      <c r="Z347" s="23"/>
       <c r="AA347" s="1"/>
       <c r="AB347" s="1"/>
       <c r="AC347" s="1"/>
@@ -27842,7 +27865,7 @@
       <c r="W348" s="1"/>
       <c r="X348" s="1"/>
       <c r="Y348" s="1"/>
-      <c r="Z348" s="1"/>
+      <c r="Z348" s="23"/>
       <c r="AA348" s="1"/>
       <c r="AB348" s="1"/>
       <c r="AC348" s="1"/>
@@ -27894,7 +27917,7 @@
       <c r="W349" s="1"/>
       <c r="X349" s="1"/>
       <c r="Y349" s="1"/>
-      <c r="Z349" s="1"/>
+      <c r="Z349" s="23"/>
       <c r="AA349" s="1"/>
       <c r="AB349" s="1"/>
       <c r="AC349" s="1"/>
@@ -27946,7 +27969,7 @@
       <c r="W350" s="1"/>
       <c r="X350" s="1"/>
       <c r="Y350" s="1"/>
-      <c r="Z350" s="1"/>
+      <c r="Z350" s="23"/>
       <c r="AA350" s="1"/>
       <c r="AB350" s="1"/>
       <c r="AC350" s="1"/>
@@ -27998,7 +28021,7 @@
       <c r="W351" s="1"/>
       <c r="X351" s="1"/>
       <c r="Y351" s="1"/>
-      <c r="Z351" s="1"/>
+      <c r="Z351" s="23"/>
       <c r="AA351" s="1"/>
       <c r="AB351" s="1"/>
       <c r="AC351" s="1"/>
@@ -28050,7 +28073,7 @@
       <c r="W352" s="1"/>
       <c r="X352" s="1"/>
       <c r="Y352" s="1"/>
-      <c r="Z352" s="1"/>
+      <c r="Z352" s="23"/>
       <c r="AA352" s="1"/>
       <c r="AB352" s="1"/>
       <c r="AC352" s="1"/>
@@ -28102,7 +28125,7 @@
       <c r="W353" s="1"/>
       <c r="X353" s="1"/>
       <c r="Y353" s="1"/>
-      <c r="Z353" s="1"/>
+      <c r="Z353" s="23"/>
       <c r="AA353" s="1"/>
       <c r="AB353" s="1"/>
       <c r="AC353" s="1"/>
@@ -28154,7 +28177,7 @@
       <c r="W354" s="1"/>
       <c r="X354" s="1"/>
       <c r="Y354" s="1"/>
-      <c r="Z354" s="1"/>
+      <c r="Z354" s="23"/>
       <c r="AA354" s="1"/>
       <c r="AB354" s="1"/>
       <c r="AC354" s="1"/>
@@ -28206,7 +28229,7 @@
       <c r="W355" s="1"/>
       <c r="X355" s="1"/>
       <c r="Y355" s="1"/>
-      <c r="Z355" s="1"/>
+      <c r="Z355" s="23"/>
       <c r="AA355" s="1"/>
       <c r="AB355" s="1"/>
       <c r="AC355" s="1"/>
@@ -28258,7 +28281,7 @@
       <c r="W356" s="1"/>
       <c r="X356" s="1"/>
       <c r="Y356" s="1"/>
-      <c r="Z356" s="1"/>
+      <c r="Z356" s="23"/>
       <c r="AA356" s="1"/>
       <c r="AB356" s="1"/>
       <c r="AC356" s="1"/>
@@ -28310,7 +28333,7 @@
       <c r="W357" s="1"/>
       <c r="X357" s="1"/>
       <c r="Y357" s="1"/>
-      <c r="Z357" s="1"/>
+      <c r="Z357" s="23"/>
       <c r="AA357" s="1"/>
       <c r="AB357" s="1"/>
       <c r="AC357" s="1"/>
@@ -28362,7 +28385,7 @@
       <c r="W358" s="1"/>
       <c r="X358" s="1"/>
       <c r="Y358" s="1"/>
-      <c r="Z358" s="1"/>
+      <c r="Z358" s="23"/>
       <c r="AA358" s="1"/>
       <c r="AB358" s="1"/>
       <c r="AC358" s="1"/>
@@ -28414,7 +28437,7 @@
       <c r="W359" s="1"/>
       <c r="X359" s="1"/>
       <c r="Y359" s="1"/>
-      <c r="Z359" s="1"/>
+      <c r="Z359" s="23"/>
       <c r="AA359" s="1"/>
       <c r="AB359" s="1"/>
       <c r="AC359" s="1"/>
@@ -28466,7 +28489,7 @@
       <c r="W360" s="1"/>
       <c r="X360" s="1"/>
       <c r="Y360" s="1"/>
-      <c r="Z360" s="1"/>
+      <c r="Z360" s="23"/>
       <c r="AA360" s="1"/>
       <c r="AB360" s="1"/>
       <c r="AC360" s="1"/>
@@ -28518,7 +28541,7 @@
       <c r="W361" s="1"/>
       <c r="X361" s="1"/>
       <c r="Y361" s="1"/>
-      <c r="Z361" s="1"/>
+      <c r="Z361" s="23"/>
       <c r="AA361" s="1"/>
       <c r="AB361" s="1"/>
       <c r="AC361" s="1"/>
@@ -28570,7 +28593,7 @@
       <c r="W362" s="1"/>
       <c r="X362" s="1"/>
       <c r="Y362" s="1"/>
-      <c r="Z362" s="1"/>
+      <c r="Z362" s="23"/>
       <c r="AA362" s="1"/>
       <c r="AB362" s="1"/>
       <c r="AC362" s="1"/>
@@ -28622,7 +28645,7 @@
       <c r="W363" s="1"/>
       <c r="X363" s="1"/>
       <c r="Y363" s="1"/>
-      <c r="Z363" s="1"/>
+      <c r="Z363" s="23"/>
       <c r="AA363" s="1"/>
       <c r="AB363" s="1"/>
       <c r="AC363" s="1"/>
@@ -28674,7 +28697,7 @@
       <c r="W364" s="1"/>
       <c r="X364" s="1"/>
       <c r="Y364" s="1"/>
-      <c r="Z364" s="1"/>
+      <c r="Z364" s="23"/>
       <c r="AA364" s="1"/>
       <c r="AB364" s="1"/>
       <c r="AC364" s="1"/>
@@ -28726,7 +28749,7 @@
       <c r="W365" s="1"/>
       <c r="X365" s="1"/>
       <c r="Y365" s="1"/>
-      <c r="Z365" s="1"/>
+      <c r="Z365" s="23"/>
       <c r="AA365" s="1"/>
       <c r="AB365" s="1"/>
       <c r="AC365" s="1"/>
@@ -28778,7 +28801,7 @@
       <c r="W366" s="1"/>
       <c r="X366" s="1"/>
       <c r="Y366" s="1"/>
-      <c r="Z366" s="1"/>
+      <c r="Z366" s="23"/>
       <c r="AA366" s="1"/>
       <c r="AB366" s="1"/>
       <c r="AC366" s="1"/>
@@ -28830,7 +28853,7 @@
       <c r="W367" s="1"/>
       <c r="X367" s="1"/>
       <c r="Y367" s="1"/>
-      <c r="Z367" s="1"/>
+      <c r="Z367" s="23"/>
       <c r="AA367" s="1"/>
       <c r="AB367" s="1"/>
       <c r="AC367" s="1"/>
@@ -28882,7 +28905,7 @@
       <c r="W368" s="1"/>
       <c r="X368" s="1"/>
       <c r="Y368" s="1"/>
-      <c r="Z368" s="1"/>
+      <c r="Z368" s="23"/>
       <c r="AA368" s="1"/>
       <c r="AB368" s="1"/>
       <c r="AC368" s="1"/>
@@ -28934,7 +28957,7 @@
       <c r="W369" s="1"/>
       <c r="X369" s="1"/>
       <c r="Y369" s="1"/>
-      <c r="Z369" s="1"/>
+      <c r="Z369" s="23"/>
       <c r="AA369" s="1"/>
       <c r="AB369" s="1"/>
       <c r="AC369" s="1"/>
@@ -28986,7 +29009,7 @@
       <c r="W370" s="1"/>
       <c r="X370" s="1"/>
       <c r="Y370" s="1"/>
-      <c r="Z370" s="1"/>
+      <c r="Z370" s="23"/>
       <c r="AA370" s="1"/>
       <c r="AB370" s="1"/>
       <c r="AC370" s="1"/>
@@ -29038,7 +29061,7 @@
       <c r="W371" s="1"/>
       <c r="X371" s="1"/>
       <c r="Y371" s="1"/>
-      <c r="Z371" s="1"/>
+      <c r="Z371" s="23"/>
       <c r="AA371" s="1"/>
       <c r="AB371" s="1"/>
       <c r="AC371" s="1"/>
@@ -29090,7 +29113,7 @@
       <c r="W372" s="1"/>
       <c r="X372" s="1"/>
       <c r="Y372" s="1"/>
-      <c r="Z372" s="1"/>
+      <c r="Z372" s="23"/>
       <c r="AA372" s="1"/>
       <c r="AB372" s="1"/>
       <c r="AC372" s="1"/>
@@ -29142,7 +29165,7 @@
       <c r="W373" s="1"/>
       <c r="X373" s="1"/>
       <c r="Y373" s="1"/>
-      <c r="Z373" s="1"/>
+      <c r="Z373" s="23"/>
       <c r="AA373" s="1"/>
       <c r="AB373" s="1"/>
       <c r="AC373" s="1"/>
@@ -29194,7 +29217,7 @@
       <c r="W374" s="1"/>
       <c r="X374" s="1"/>
       <c r="Y374" s="1"/>
-      <c r="Z374" s="1"/>
+      <c r="Z374" s="23"/>
       <c r="AA374" s="1"/>
       <c r="AB374" s="1"/>
       <c r="AC374" s="1"/>
@@ -29246,7 +29269,7 @@
       <c r="W375" s="1"/>
       <c r="X375" s="1"/>
       <c r="Y375" s="1"/>
-      <c r="Z375" s="1"/>
+      <c r="Z375" s="23"/>
       <c r="AA375" s="1"/>
       <c r="AB375" s="1"/>
       <c r="AC375" s="1"/>
@@ -29298,7 +29321,7 @@
       <c r="W376" s="1"/>
       <c r="X376" s="1"/>
       <c r="Y376" s="1"/>
-      <c r="Z376" s="1"/>
+      <c r="Z376" s="23"/>
       <c r="AA376" s="1"/>
       <c r="AB376" s="1"/>
       <c r="AC376" s="1"/>
@@ -29350,7 +29373,7 @@
       <c r="W377" s="1"/>
       <c r="X377" s="1"/>
       <c r="Y377" s="1"/>
-      <c r="Z377" s="1"/>
+      <c r="Z377" s="23"/>
       <c r="AA377" s="1"/>
       <c r="AB377" s="1"/>
       <c r="AC377" s="1"/>
@@ -29402,7 +29425,7 @@
       <c r="W378" s="1"/>
       <c r="X378" s="1"/>
       <c r="Y378" s="1"/>
-      <c r="Z378" s="1"/>
+      <c r="Z378" s="23"/>
       <c r="AA378" s="1"/>
       <c r="AB378" s="1"/>
       <c r="AC378" s="1"/>
@@ -29454,7 +29477,7 @@
       <c r="W379" s="1"/>
       <c r="X379" s="1"/>
       <c r="Y379" s="1"/>
-      <c r="Z379" s="1"/>
+      <c r="Z379" s="23"/>
       <c r="AA379" s="1"/>
       <c r="AB379" s="1"/>
       <c r="AC379" s="1"/>
@@ -29506,7 +29529,7 @@
       <c r="W380" s="1"/>
       <c r="X380" s="1"/>
       <c r="Y380" s="1"/>
-      <c r="Z380" s="1"/>
+      <c r="Z380" s="23"/>
       <c r="AA380" s="1"/>
       <c r="AB380" s="1"/>
       <c r="AC380" s="1"/>
@@ -29558,7 +29581,7 @@
       <c r="W381" s="1"/>
       <c r="X381" s="1"/>
       <c r="Y381" s="1"/>
-      <c r="Z381" s="1"/>
+      <c r="Z381" s="23"/>
       <c r="AA381" s="1"/>
       <c r="AB381" s="1"/>
       <c r="AC381" s="1"/>
@@ -29610,7 +29633,7 @@
       <c r="W382" s="1"/>
       <c r="X382" s="1"/>
       <c r="Y382" s="1"/>
-      <c r="Z382" s="1"/>
+      <c r="Z382" s="23"/>
       <c r="AA382" s="1"/>
       <c r="AB382" s="1"/>
       <c r="AC382" s="1"/>
@@ -29662,7 +29685,7 @@
       <c r="W383" s="1"/>
       <c r="X383" s="1"/>
       <c r="Y383" s="1"/>
-      <c r="Z383" s="1"/>
+      <c r="Z383" s="23"/>
       <c r="AA383" s="1"/>
       <c r="AB383" s="1"/>
       <c r="AC383" s="1"/>
@@ -29714,7 +29737,7 @@
       <c r="W384" s="1"/>
       <c r="X384" s="1"/>
       <c r="Y384" s="1"/>
-      <c r="Z384" s="1"/>
+      <c r="Z384" s="23"/>
       <c r="AA384" s="1"/>
       <c r="AB384" s="1"/>
       <c r="AC384" s="1"/>
@@ -29766,7 +29789,7 @@
       <c r="W385" s="1"/>
       <c r="X385" s="1"/>
       <c r="Y385" s="1"/>
-      <c r="Z385" s="1"/>
+      <c r="Z385" s="23"/>
       <c r="AA385" s="1"/>
       <c r="AB385" s="1"/>
       <c r="AC385" s="1"/>
@@ -29818,7 +29841,7 @@
       <c r="W386" s="1"/>
       <c r="X386" s="1"/>
       <c r="Y386" s="1"/>
-      <c r="Z386" s="1"/>
+      <c r="Z386" s="23"/>
       <c r="AA386" s="1"/>
       <c r="AB386" s="1"/>
       <c r="AC386" s="1"/>
@@ -29870,7 +29893,7 @@
       <c r="W387" s="1"/>
       <c r="X387" s="1"/>
       <c r="Y387" s="1"/>
-      <c r="Z387" s="1"/>
+      <c r="Z387" s="23"/>
       <c r="AA387" s="1"/>
       <c r="AB387" s="1"/>
       <c r="AC387" s="1"/>
@@ -29922,7 +29945,7 @@
       <c r="W388" s="1"/>
       <c r="X388" s="1"/>
       <c r="Y388" s="1"/>
-      <c r="Z388" s="1"/>
+      <c r="Z388" s="23"/>
       <c r="AA388" s="1"/>
       <c r="AB388" s="1"/>
       <c r="AC388" s="1"/>
@@ -29974,7 +29997,7 @@
       <c r="W389" s="1"/>
       <c r="X389" s="1"/>
       <c r="Y389" s="1"/>
-      <c r="Z389" s="1"/>
+      <c r="Z389" s="23"/>
       <c r="AA389" s="1"/>
       <c r="AB389" s="1"/>
       <c r="AC389" s="1"/>
@@ -30026,7 +30049,7 @@
       <c r="W390" s="1"/>
       <c r="X390" s="1"/>
       <c r="Y390" s="1"/>
-      <c r="Z390" s="1"/>
+      <c r="Z390" s="23"/>
       <c r="AA390" s="1"/>
       <c r="AB390" s="1"/>
       <c r="AC390" s="1"/>
@@ -30078,7 +30101,7 @@
       <c r="W391" s="1"/>
       <c r="X391" s="1"/>
       <c r="Y391" s="1"/>
-      <c r="Z391" s="1"/>
+      <c r="Z391" s="23"/>
       <c r="AA391" s="1"/>
       <c r="AB391" s="1"/>
       <c r="AC391" s="1"/>
@@ -30130,7 +30153,7 @@
       <c r="W392" s="1"/>
       <c r="X392" s="1"/>
       <c r="Y392" s="1"/>
-      <c r="Z392" s="1"/>
+      <c r="Z392" s="23"/>
       <c r="AA392" s="1"/>
       <c r="AB392" s="1"/>
       <c r="AC392" s="1"/>
@@ -30182,7 +30205,7 @@
       <c r="W393" s="1"/>
       <c r="X393" s="1"/>
       <c r="Y393" s="1"/>
-      <c r="Z393" s="1"/>
+      <c r="Z393" s="23"/>
       <c r="AA393" s="1"/>
       <c r="AB393" s="1"/>
       <c r="AC393" s="1"/>
@@ -30234,7 +30257,7 @@
       <c r="W394" s="1"/>
       <c r="X394" s="1"/>
       <c r="Y394" s="1"/>
-      <c r="Z394" s="1"/>
+      <c r="Z394" s="23"/>
       <c r="AA394" s="1"/>
       <c r="AB394" s="1"/>
       <c r="AC394" s="1"/>
@@ -30286,7 +30309,7 @@
       <c r="W395" s="1"/>
       <c r="X395" s="1"/>
       <c r="Y395" s="1"/>
-      <c r="Z395" s="1"/>
+      <c r="Z395" s="23"/>
       <c r="AA395" s="1"/>
       <c r="AB395" s="1"/>
       <c r="AC395" s="1"/>
@@ -30338,7 +30361,7 @@
       <c r="W396" s="1"/>
       <c r="X396" s="1"/>
       <c r="Y396" s="1"/>
-      <c r="Z396" s="1"/>
+      <c r="Z396" s="23"/>
       <c r="AA396" s="1"/>
       <c r="AB396" s="1"/>
       <c r="AC396" s="1"/>
@@ -30390,7 +30413,7 @@
       <c r="W397" s="1"/>
       <c r="X397" s="1"/>
       <c r="Y397" s="1"/>
-      <c r="Z397" s="1"/>
+      <c r="Z397" s="23"/>
       <c r="AA397" s="1"/>
       <c r="AB397" s="1"/>
       <c r="AC397" s="1"/>
@@ -30442,7 +30465,7 @@
       <c r="W398" s="1"/>
       <c r="X398" s="1"/>
       <c r="Y398" s="1"/>
-      <c r="Z398" s="1"/>
+      <c r="Z398" s="23"/>
       <c r="AA398" s="1"/>
       <c r="AB398" s="1"/>
       <c r="AC398" s="1"/>
@@ -30494,7 +30517,7 @@
       <c r="W399" s="1"/>
       <c r="X399" s="1"/>
       <c r="Y399" s="1"/>
-      <c r="Z399" s="1"/>
+      <c r="Z399" s="23"/>
       <c r="AA399" s="1"/>
       <c r="AB399" s="1"/>
       <c r="AC399" s="1"/>
@@ -30546,7 +30569,7 @@
       <c r="W400" s="1"/>
       <c r="X400" s="1"/>
       <c r="Y400" s="1"/>
-      <c r="Z400" s="1"/>
+      <c r="Z400" s="23"/>
       <c r="AA400" s="1"/>
       <c r="AB400" s="1"/>
       <c r="AC400" s="1"/>
@@ -30598,7 +30621,7 @@
       <c r="W401" s="1"/>
       <c r="X401" s="1"/>
       <c r="Y401" s="1"/>
-      <c r="Z401" s="1"/>
+      <c r="Z401" s="23"/>
       <c r="AA401" s="1"/>
       <c r="AB401" s="1"/>
       <c r="AC401" s="1"/>
@@ -30650,7 +30673,7 @@
       <c r="W402" s="1"/>
       <c r="X402" s="1"/>
       <c r="Y402" s="1"/>
-      <c r="Z402" s="1"/>
+      <c r="Z402" s="23"/>
       <c r="AA402" s="1"/>
       <c r="AB402" s="1"/>
       <c r="AC402" s="1"/>
@@ -30702,7 +30725,7 @@
       <c r="W403" s="1"/>
       <c r="X403" s="1"/>
       <c r="Y403" s="1"/>
-      <c r="Z403" s="1"/>
+      <c r="Z403" s="23"/>
       <c r="AA403" s="1"/>
       <c r="AB403" s="1"/>
       <c r="AC403" s="1"/>
@@ -30754,7 +30777,7 @@
       <c r="W404" s="1"/>
       <c r="X404" s="1"/>
       <c r="Y404" s="1"/>
-      <c r="Z404" s="1"/>
+      <c r="Z404" s="23"/>
       <c r="AA404" s="1"/>
       <c r="AB404" s="1"/>
       <c r="AC404" s="1"/>
@@ -30806,7 +30829,7 @@
       <c r="W405" s="1"/>
       <c r="X405" s="1"/>
       <c r="Y405" s="1"/>
-      <c r="Z405" s="1"/>
+      <c r="Z405" s="23"/>
       <c r="AA405" s="1"/>
       <c r="AB405" s="1"/>
       <c r="AC405" s="1"/>
@@ -30858,7 +30881,7 @@
       <c r="W406" s="1"/>
       <c r="X406" s="1"/>
       <c r="Y406" s="1"/>
-      <c r="Z406" s="1"/>
+      <c r="Z406" s="23"/>
       <c r="AA406" s="1"/>
       <c r="AB406" s="1"/>
       <c r="AC406" s="1"/>
@@ -30910,7 +30933,7 @@
       <c r="W407" s="1"/>
       <c r="X407" s="1"/>
       <c r="Y407" s="1"/>
-      <c r="Z407" s="1"/>
+      <c r="Z407" s="23"/>
       <c r="AA407" s="1"/>
       <c r="AB407" s="1"/>
       <c r="AC407" s="1"/>
@@ -30962,7 +30985,7 @@
       <c r="W408" s="1"/>
       <c r="X408" s="1"/>
       <c r="Y408" s="1"/>
-      <c r="Z408" s="1"/>
+      <c r="Z408" s="23"/>
       <c r="AA408" s="1"/>
       <c r="AB408" s="1"/>
       <c r="AC408" s="1"/>
@@ -31014,7 +31037,7 @@
       <c r="W409" s="1"/>
       <c r="X409" s="1"/>
       <c r="Y409" s="1"/>
-      <c r="Z409" s="1"/>
+      <c r="Z409" s="23"/>
       <c r="AA409" s="1"/>
       <c r="AB409" s="1"/>
       <c r="AC409" s="1"/>
@@ -31066,7 +31089,7 @@
       <c r="W410" s="1"/>
       <c r="X410" s="1"/>
       <c r="Y410" s="1"/>
-      <c r="Z410" s="1"/>
+      <c r="Z410" s="23"/>
       <c r="AA410" s="1"/>
       <c r="AB410" s="1"/>
       <c r="AC410" s="1"/>
@@ -31118,7 +31141,7 @@
       <c r="W411" s="1"/>
       <c r="X411" s="1"/>
       <c r="Y411" s="1"/>
-      <c r="Z411" s="1"/>
+      <c r="Z411" s="23"/>
       <c r="AA411" s="1"/>
       <c r="AB411" s="1"/>
       <c r="AC411" s="1"/>
@@ -31170,7 +31193,7 @@
       <c r="W412" s="1"/>
       <c r="X412" s="1"/>
       <c r="Y412" s="1"/>
-      <c r="Z412" s="1"/>
+      <c r="Z412" s="23"/>
       <c r="AA412" s="1"/>
       <c r="AB412" s="1"/>
       <c r="AC412" s="1"/>
@@ -31222,7 +31245,7 @@
       <c r="W413" s="1"/>
       <c r="X413" s="1"/>
       <c r="Y413" s="1"/>
-      <c r="Z413" s="1"/>
+      <c r="Z413" s="23"/>
       <c r="AA413" s="1"/>
       <c r="AB413" s="1"/>
       <c r="AC413" s="1"/>
@@ -31274,7 +31297,7 @@
       <c r="W414" s="1"/>
       <c r="X414" s="1"/>
       <c r="Y414" s="1"/>
-      <c r="Z414" s="1"/>
+      <c r="Z414" s="23"/>
       <c r="AA414" s="1"/>
       <c r="AB414" s="1"/>
       <c r="AC414" s="1"/>
@@ -31326,7 +31349,7 @@
       <c r="W415" s="1"/>
       <c r="X415" s="1"/>
       <c r="Y415" s="1"/>
-      <c r="Z415" s="1"/>
+      <c r="Z415" s="23"/>
       <c r="AA415" s="1"/>
       <c r="AB415" s="1"/>
       <c r="AC415" s="1"/>
@@ -31378,7 +31401,7 @@
       <c r="W416" s="1"/>
       <c r="X416" s="1"/>
       <c r="Y416" s="1"/>
-      <c r="Z416" s="1"/>
+      <c r="Z416" s="23"/>
       <c r="AA416" s="1"/>
       <c r="AB416" s="1"/>
       <c r="AC416" s="1"/>
@@ -31430,7 +31453,7 @@
       <c r="W417" s="1"/>
       <c r="X417" s="1"/>
       <c r="Y417" s="1"/>
-      <c r="Z417" s="1"/>
+      <c r="Z417" s="23"/>
       <c r="AA417" s="1"/>
       <c r="AB417" s="1"/>
       <c r="AC417" s="1"/>
@@ -31482,7 +31505,7 @@
       <c r="W418" s="1"/>
       <c r="X418" s="1"/>
       <c r="Y418" s="1"/>
-      <c r="Z418" s="1"/>
+      <c r="Z418" s="23"/>
       <c r="AA418" s="1"/>
       <c r="AB418" s="1"/>
       <c r="AC418" s="1"/>
@@ -31534,7 +31557,7 @@
       <c r="W419" s="1"/>
       <c r="X419" s="1"/>
       <c r="Y419" s="1"/>
-      <c r="Z419" s="1"/>
+      <c r="Z419" s="23"/>
       <c r="AA419" s="1"/>
       <c r="AB419" s="1"/>
       <c r="AC419" s="1"/>
@@ -31586,7 +31609,7 @@
       <c r="W420" s="1"/>
       <c r="X420" s="1"/>
       <c r="Y420" s="1"/>
-      <c r="Z420" s="1"/>
+      <c r="Z420" s="23"/>
       <c r="AA420" s="1"/>
       <c r="AB420" s="1"/>
       <c r="AC420" s="1"/>
@@ -31638,7 +31661,7 @@
       <c r="W421" s="1"/>
       <c r="X421" s="1"/>
       <c r="Y421" s="1"/>
-      <c r="Z421" s="1"/>
+      <c r="Z421" s="23"/>
       <c r="AA421" s="1"/>
       <c r="AB421" s="1"/>
       <c r="AC421" s="1"/>
@@ -31690,7 +31713,7 @@
       <c r="W422" s="1"/>
       <c r="X422" s="1"/>
       <c r="Y422" s="1"/>
-      <c r="Z422" s="1"/>
+      <c r="Z422" s="23"/>
       <c r="AA422" s="1"/>
       <c r="AB422" s="1"/>
       <c r="AC422" s="1"/>
@@ -31742,7 +31765,7 @@
       <c r="W423" s="1"/>
       <c r="X423" s="1"/>
       <c r="Y423" s="1"/>
-      <c r="Z423" s="1"/>
+      <c r="Z423" s="23"/>
       <c r="AA423" s="1"/>
       <c r="AB423" s="1"/>
       <c r="AC423" s="1"/>
@@ -31794,7 +31817,7 @@
       <c r="W424" s="1"/>
       <c r="X424" s="1"/>
       <c r="Y424" s="1"/>
-      <c r="Z424" s="1"/>
+      <c r="Z424" s="23"/>
       <c r="AA424" s="1"/>
       <c r="AB424" s="1"/>
       <c r="AC424" s="1"/>
@@ -31846,7 +31869,7 @@
       <c r="W425" s="1"/>
       <c r="X425" s="1"/>
       <c r="Y425" s="1"/>
-      <c r="Z425" s="1"/>
+      <c r="Z425" s="23"/>
       <c r="AA425" s="1"/>
       <c r="AB425" s="1"/>
       <c r="AC425" s="1"/>
@@ -31898,7 +31921,7 @@
       <c r="W426" s="1"/>
       <c r="X426" s="1"/>
       <c r="Y426" s="1"/>
-      <c r="Z426" s="1"/>
+      <c r="Z426" s="23"/>
       <c r="AA426" s="1"/>
       <c r="AB426" s="1"/>
       <c r="AC426" s="1"/>
@@ -31950,7 +31973,7 @@
       <c r="W427" s="1"/>
       <c r="X427" s="1"/>
       <c r="Y427" s="1"/>
-      <c r="Z427" s="1"/>
+      <c r="Z427" s="23"/>
       <c r="AA427" s="1"/>
       <c r="AB427" s="1"/>
       <c r="AC427" s="1"/>
@@ -32002,7 +32025,7 @@
       <c r="W428" s="1"/>
       <c r="X428" s="1"/>
       <c r="Y428" s="1"/>
-      <c r="Z428" s="1"/>
+      <c r="Z428" s="23"/>
       <c r="AA428" s="1"/>
       <c r="AB428" s="1"/>
       <c r="AC428" s="1"/>
@@ -32054,7 +32077,7 @@
       <c r="W429" s="1"/>
       <c r="X429" s="1"/>
       <c r="Y429" s="1"/>
-      <c r="Z429" s="1"/>
+      <c r="Z429" s="23"/>
       <c r="AA429" s="1"/>
       <c r="AB429" s="1"/>
       <c r="AC429" s="1"/>
@@ -32106,7 +32129,7 @@
       <c r="W430" s="1"/>
       <c r="X430" s="1"/>
       <c r="Y430" s="1"/>
-      <c r="Z430" s="1"/>
+      <c r="Z430" s="23"/>
       <c r="AA430" s="1"/>
       <c r="AB430" s="1"/>
       <c r="AC430" s="1"/>
@@ -32158,7 +32181,7 @@
       <c r="W431" s="1"/>
       <c r="X431" s="1"/>
       <c r="Y431" s="1"/>
-      <c r="Z431" s="1"/>
+      <c r="Z431" s="23"/>
       <c r="AA431" s="1"/>
       <c r="AB431" s="1"/>
       <c r="AC431" s="1"/>
@@ -32210,7 +32233,7 @@
       <c r="W432" s="1"/>
       <c r="X432" s="1"/>
       <c r="Y432" s="1"/>
-      <c r="Z432" s="1"/>
+      <c r="Z432" s="23"/>
       <c r="AA432" s="1"/>
       <c r="AB432" s="1"/>
       <c r="AC432" s="1"/>
@@ -32262,7 +32285,7 @@
       <c r="W433" s="1"/>
       <c r="X433" s="1"/>
       <c r="Y433" s="1"/>
-      <c r="Z433" s="1"/>
+      <c r="Z433" s="23"/>
       <c r="AA433" s="1"/>
       <c r="AB433" s="1"/>
       <c r="AC433" s="1"/>
@@ -32314,7 +32337,7 @@
       <c r="W434" s="1"/>
       <c r="X434" s="1"/>
       <c r="Y434" s="1"/>
-      <c r="Z434" s="1"/>
+      <c r="Z434" s="23"/>
       <c r="AA434" s="1"/>
       <c r="AB434" s="1"/>
       <c r="AC434" s="1"/>
@@ -32366,7 +32389,7 @@
       <c r="W435" s="1"/>
       <c r="X435" s="1"/>
       <c r="Y435" s="1"/>
-      <c r="Z435" s="1"/>
+      <c r="Z435" s="23"/>
       <c r="AA435" s="1"/>
       <c r="AB435" s="1"/>
       <c r="AC435" s="1"/>
@@ -32418,7 +32441,7 @@
       <c r="W436" s="1"/>
       <c r="X436" s="1"/>
       <c r="Y436" s="1"/>
-      <c r="Z436" s="1"/>
+      <c r="Z436" s="23"/>
       <c r="AA436" s="1"/>
       <c r="AB436" s="1"/>
       <c r="AC436" s="1"/>
@@ -32470,7 +32493,7 @@
       <c r="W437" s="1"/>
       <c r="X437" s="1"/>
       <c r="Y437" s="1"/>
-      <c r="Z437" s="1"/>
+      <c r="Z437" s="23"/>
       <c r="AA437" s="1"/>
       <c r="AB437" s="1"/>
       <c r="AC437" s="1"/>
@@ -32522,7 +32545,7 @@
       <c r="W438" s="1"/>
       <c r="X438" s="1"/>
       <c r="Y438" s="1"/>
-      <c r="Z438" s="1"/>
+      <c r="Z438" s="23"/>
       <c r="AA438" s="1"/>
       <c r="AB438" s="1"/>
       <c r="AC438" s="1"/>
@@ -32574,7 +32597,7 @@
       <c r="W439" s="1"/>
       <c r="X439" s="1"/>
       <c r="Y439" s="1"/>
-      <c r="Z439" s="1"/>
+      <c r="Z439" s="23"/>
       <c r="AA439" s="1"/>
       <c r="AB439" s="1"/>
       <c r="AC439" s="1"/>
@@ -32626,7 +32649,7 @@
       <c r="W440" s="1"/>
       <c r="X440" s="1"/>
       <c r="Y440" s="1"/>
-      <c r="Z440" s="1"/>
+      <c r="Z440" s="23"/>
       <c r="AA440" s="1"/>
       <c r="AB440" s="1"/>
       <c r="AC440" s="1"/>
@@ -32678,7 +32701,7 @@
       <c r="W441" s="1"/>
       <c r="X441" s="1"/>
       <c r="Y441" s="1"/>
-      <c r="Z441" s="1"/>
+      <c r="Z441" s="23"/>
       <c r="AA441" s="1"/>
       <c r="AB441" s="1"/>
       <c r="AC441" s="1"/>
@@ -32730,7 +32753,7 @@
       <c r="W442" s="1"/>
       <c r="X442" s="1"/>
       <c r="Y442" s="1"/>
-      <c r="Z442" s="1"/>
+      <c r="Z442" s="23"/>
       <c r="AA442" s="1"/>
       <c r="AB442" s="1"/>
       <c r="AC442" s="1"/>
@@ -32782,7 +32805,7 @@
       <c r="W443" s="1"/>
       <c r="X443" s="1"/>
       <c r="Y443" s="1"/>
-      <c r="Z443" s="1"/>
+      <c r="Z443" s="23"/>
       <c r="AA443" s="1"/>
       <c r="AB443" s="1"/>
       <c r="AC443" s="1"/>
@@ -32834,7 +32857,7 @@
       <c r="W444" s="1"/>
       <c r="X444" s="1"/>
       <c r="Y444" s="1"/>
-      <c r="Z444" s="1"/>
+      <c r="Z444" s="23"/>
       <c r="AA444" s="1"/>
       <c r="AB444" s="1"/>
       <c r="AC444" s="1"/>
@@ -32886,7 +32909,7 @@
       <c r="W445" s="1"/>
       <c r="X445" s="1"/>
       <c r="Y445" s="1"/>
-      <c r="Z445" s="1"/>
+      <c r="Z445" s="23"/>
       <c r="AA445" s="1"/>
       <c r="AB445" s="1"/>
       <c r="AC445" s="1"/>
@@ -32938,7 +32961,7 @@
       <c r="W446" s="1"/>
       <c r="X446" s="1"/>
       <c r="Y446" s="1"/>
-      <c r="Z446" s="1"/>
+      <c r="Z446" s="23"/>
       <c r="AA446" s="1"/>
       <c r="AB446" s="1"/>
       <c r="AC446" s="1"/>
@@ -32990,7 +33013,7 @@
       <c r="W447" s="1"/>
       <c r="X447" s="1"/>
       <c r="Y447" s="1"/>
-      <c r="Z447" s="1"/>
+      <c r="Z447" s="23"/>
       <c r="AA447" s="1"/>
       <c r="AB447" s="1"/>
       <c r="AC447" s="1"/>
@@ -33042,7 +33065,7 @@
       <c r="W448" s="1"/>
       <c r="X448" s="1"/>
       <c r="Y448" s="1"/>
-      <c r="Z448" s="1"/>
+      <c r="Z448" s="23"/>
       <c r="AA448" s="1"/>
       <c r="AB448" s="1"/>
       <c r="AC448" s="1"/>
@@ -33094,7 +33117,7 @@
       <c r="W449" s="1"/>
       <c r="X449" s="1"/>
       <c r="Y449" s="1"/>
-      <c r="Z449" s="1"/>
+      <c r="Z449" s="23"/>
       <c r="AA449" s="1"/>
       <c r="AB449" s="1"/>
       <c r="AC449" s="1"/>
@@ -33146,7 +33169,7 @@
       <c r="W450" s="1"/>
       <c r="X450" s="1"/>
       <c r="Y450" s="1"/>
-      <c r="Z450" s="1"/>
+      <c r="Z450" s="23"/>
       <c r="AA450" s="1"/>
       <c r="AB450" s="1"/>
       <c r="AC450" s="1"/>
@@ -33198,7 +33221,7 @@
       <c r="W451" s="1"/>
       <c r="X451" s="1"/>
       <c r="Y451" s="1"/>
-      <c r="Z451" s="1"/>
+      <c r="Z451" s="23"/>
       <c r="AA451" s="1"/>
       <c r="AB451" s="1"/>
       <c r="AC451" s="1"/>
@@ -33250,7 +33273,7 @@
       <c r="W452" s="1"/>
       <c r="X452" s="1"/>
       <c r="Y452" s="1"/>
-      <c r="Z452" s="1"/>
+      <c r="Z452" s="23"/>
       <c r="AA452" s="1"/>
       <c r="AB452" s="1"/>
       <c r="AC452" s="1"/>
@@ -33302,7 +33325,7 @@
       <c r="W453" s="1"/>
       <c r="X453" s="1"/>
       <c r="Y453" s="1"/>
-      <c r="Z453" s="1"/>
+      <c r="Z453" s="23"/>
       <c r="AA453" s="1"/>
       <c r="AB453" s="1"/>
       <c r="AC453" s="1"/>
@@ -33354,7 +33377,7 @@
       <c r="W454" s="1"/>
       <c r="X454" s="1"/>
       <c r="Y454" s="1"/>
-      <c r="Z454" s="1"/>
+      <c r="Z454" s="23"/>
       <c r="AA454" s="1"/>
       <c r="AB454" s="1"/>
       <c r="AC454" s="1"/>
@@ -33406,7 +33429,7 @@
       <c r="W455" s="1"/>
       <c r="X455" s="1"/>
       <c r="Y455" s="1"/>
-      <c r="Z455" s="1"/>
+      <c r="Z455" s="23"/>
       <c r="AA455" s="1"/>
       <c r="AB455" s="1"/>
       <c r="AC455" s="1"/>
@@ -33458,7 +33481,7 @@
       <c r="W456" s="1"/>
       <c r="X456" s="1"/>
       <c r="Y456" s="1"/>
-      <c r="Z456" s="1"/>
+      <c r="Z456" s="23"/>
       <c r="AA456" s="1"/>
       <c r="AB456" s="1"/>
       <c r="AC456" s="1"/>
@@ -33510,7 +33533,7 @@
       <c r="W457" s="1"/>
       <c r="X457" s="1"/>
       <c r="Y457" s="1"/>
-      <c r="Z457" s="1"/>
+      <c r="Z457" s="23"/>
       <c r="AA457" s="1"/>
       <c r="AB457" s="1"/>
       <c r="AC457" s="1"/>
@@ -33562,7 +33585,7 @@
       <c r="W458" s="1"/>
       <c r="X458" s="1"/>
       <c r="Y458" s="1"/>
-      <c r="Z458" s="1"/>
+      <c r="Z458" s="23"/>
       <c r="AA458" s="1"/>
       <c r="AB458" s="1"/>
       <c r="AC458" s="1"/>
@@ -33614,7 +33637,7 @@
       <c r="W459" s="1"/>
       <c r="X459" s="1"/>
       <c r="Y459" s="1"/>
-      <c r="Z459" s="1"/>
+      <c r="Z459" s="23"/>
       <c r="AA459" s="1"/>
       <c r="AB459" s="1"/>
       <c r="AC459" s="1"/>
@@ -33666,7 +33689,7 @@
       <c r="W460" s="1"/>
       <c r="X460" s="1"/>
       <c r="Y460" s="1"/>
-      <c r="Z460" s="1"/>
+      <c r="Z460" s="23"/>
       <c r="AA460" s="1"/>
       <c r="AB460" s="1"/>
       <c r="AC460" s="1"/>
@@ -33718,7 +33741,7 @@
       <c r="W461" s="1"/>
       <c r="X461" s="1"/>
       <c r="Y461" s="1"/>
-      <c r="Z461" s="1"/>
+      <c r="Z461" s="23"/>
       <c r="AA461" s="1"/>
       <c r="AB461" s="1"/>
       <c r="AC461" s="1"/>
@@ -33770,7 +33793,7 @@
       <c r="W462" s="1"/>
       <c r="X462" s="1"/>
       <c r="Y462" s="1"/>
-      <c r="Z462" s="1"/>
+      <c r="Z462" s="23"/>
       <c r="AA462" s="1"/>
       <c r="AB462" s="1"/>
       <c r="AC462" s="1"/>
@@ -33822,7 +33845,7 @@
       <c r="W463" s="1"/>
       <c r="X463" s="1"/>
       <c r="Y463" s="1"/>
-      <c r="Z463" s="1"/>
+      <c r="Z463" s="23"/>
       <c r="AA463" s="1"/>
       <c r="AB463" s="1"/>
       <c r="AC463" s="1"/>
@@ -33874,7 +33897,7 @@
       <c r="W464" s="1"/>
       <c r="X464" s="1"/>
       <c r="Y464" s="1"/>
-      <c r="Z464" s="1"/>
+      <c r="Z464" s="23"/>
       <c r="AA464" s="1"/>
       <c r="AB464" s="1"/>
       <c r="AC464" s="1"/>
@@ -33926,7 +33949,7 @@
       <c r="W465" s="1"/>
       <c r="X465" s="1"/>
       <c r="Y465" s="1"/>
-      <c r="Z465" s="1"/>
+      <c r="Z465" s="23"/>
       <c r="AA465" s="1"/>
       <c r="AB465" s="1"/>
       <c r="AC465" s="1"/>
@@ -33978,7 +34001,7 @@
       <c r="W466" s="1"/>
       <c r="X466" s="1"/>
       <c r="Y466" s="1"/>
-      <c r="Z466" s="1"/>
+      <c r="Z466" s="23"/>
       <c r="AA466" s="1"/>
       <c r="AB466" s="1"/>
       <c r="AC466" s="1"/>
@@ -34030,7 +34053,7 @@
       <c r="W467" s="1"/>
       <c r="X467" s="1"/>
       <c r="Y467" s="1"/>
-      <c r="Z467" s="1"/>
+      <c r="Z467" s="23"/>
       <c r="AA467" s="1"/>
       <c r="AB467" s="1"/>
       <c r="AC467" s="1"/>
@@ -34082,7 +34105,7 @@
       <c r="W468" s="1"/>
       <c r="X468" s="1"/>
       <c r="Y468" s="1"/>
-      <c r="Z468" s="1"/>
+      <c r="Z468" s="23"/>
       <c r="AA468" s="1"/>
       <c r="AB468" s="1"/>
       <c r="AC468" s="1"/>
@@ -34134,7 +34157,7 @@
       <c r="W469" s="1"/>
       <c r="X469" s="1"/>
       <c r="Y469" s="1"/>
-      <c r="Z469" s="1"/>
+      <c r="Z469" s="23"/>
       <c r="AA469" s="1"/>
       <c r="AB469" s="1"/>
       <c r="AC469" s="1"/>
@@ -34186,7 +34209,7 @@
       <c r="W470" s="1"/>
       <c r="X470" s="1"/>
       <c r="Y470" s="1"/>
-      <c r="Z470" s="1"/>
+      <c r="Z470" s="23"/>
       <c r="AA470" s="1"/>
       <c r="AB470" s="1"/>
       <c r="AC470" s="1"/>
@@ -34238,7 +34261,7 @@
       <c r="W471" s="1"/>
       <c r="X471" s="1"/>
       <c r="Y471" s="1"/>
-      <c r="Z471" s="1"/>
+      <c r="Z471" s="23"/>
       <c r="AA471" s="1"/>
       <c r="AB471" s="1"/>
       <c r="AC471" s="1"/>
@@ -34290,7 +34313,7 @@
       <c r="W472" s="1"/>
       <c r="X472" s="1"/>
       <c r="Y472" s="1"/>
-      <c r="Z472" s="1"/>
+      <c r="Z472" s="23"/>
       <c r="AA472" s="1"/>
       <c r="AB472" s="1"/>
       <c r="AC472" s="1"/>
@@ -34342,7 +34365,7 @@
       <c r="W473" s="1"/>
       <c r="X473" s="1"/>
       <c r="Y473" s="1"/>
-      <c r="Z473" s="1"/>
+      <c r="Z473" s="23"/>
       <c r="AA473" s="1"/>
       <c r="AB473" s="1"/>
       <c r="AC473" s="1"/>
@@ -34394,7 +34417,7 @@
       <c r="W474" s="1"/>
       <c r="X474" s="1"/>
       <c r="Y474" s="1"/>
-      <c r="Z474" s="1"/>
+      <c r="Z474" s="23"/>
       <c r="AA474" s="1"/>
       <c r="AB474" s="1"/>
       <c r="AC474" s="1"/>
@@ -34446,7 +34469,7 @@
       <c r="W475" s="1"/>
       <c r="X475" s="1"/>
       <c r="Y475" s="1"/>
-      <c r="Z475" s="1"/>
+      <c r="Z475" s="23"/>
       <c r="AA475" s="1"/>
       <c r="AB475" s="1"/>
       <c r="AC475" s="1"/>
@@ -34498,7 +34521,7 @@
       <c r="W476" s="1"/>
       <c r="X476" s="1"/>
       <c r="Y476" s="1"/>
-      <c r="Z476" s="1"/>
+      <c r="Z476" s="23"/>
       <c r="AA476" s="1"/>
       <c r="AB476" s="1"/>
       <c r="AC476" s="1"/>
@@ -34550,7 +34573,7 @@
       <c r="W477" s="1"/>
       <c r="X477" s="1"/>
       <c r="Y477" s="1"/>
-      <c r="Z477" s="1"/>
+      <c r="Z477" s="23"/>
       <c r="AA477" s="1"/>
       <c r="AB477" s="1"/>
       <c r="AC477" s="1"/>
@@ -34602,7 +34625,7 @@
       <c r="W478" s="1"/>
       <c r="X478" s="1"/>
       <c r="Y478" s="1"/>
-      <c r="Z478" s="1"/>
+      <c r="Z478" s="23"/>
       <c r="AA478" s="1"/>
       <c r="AB478" s="1"/>
       <c r="AC478" s="1"/>
@@ -34654,7 +34677,7 @@
       <c r="W479" s="1"/>
       <c r="X479" s="1"/>
       <c r="Y479" s="1"/>
-      <c r="Z479" s="1"/>
+      <c r="Z479" s="23"/>
       <c r="AA479" s="1"/>
       <c r="AB479" s="1"/>
       <c r="AC479" s="1"/>
@@ -34706,7 +34729,7 @@
       <c r="W480" s="1"/>
       <c r="X480" s="1"/>
       <c r="Y480" s="1"/>
-      <c r="Z480" s="1"/>
+      <c r="Z480" s="23"/>
       <c r="AA480" s="1"/>
       <c r="AB480" s="1"/>
       <c r="AC480" s="1"/>
@@ -34758,7 +34781,7 @@
       <c r="W481" s="1"/>
       <c r="X481" s="1"/>
       <c r="Y481" s="1"/>
-      <c r="Z481" s="1"/>
+      <c r="Z481" s="23"/>
       <c r="AA481" s="1"/>
       <c r="AB481" s="1"/>
       <c r="AC481" s="1"/>
@@ -34810,7 +34833,7 @@
       <c r="W482" s="1"/>
       <c r="X482" s="1"/>
       <c r="Y482" s="1"/>
-      <c r="Z482" s="1"/>
+      <c r="Z482" s="23"/>
       <c r="AA482" s="1"/>
       <c r="AB482" s="1"/>
       <c r="AC482" s="1"/>
@@ -34862,7 +34885,7 @@
       <c r="W483" s="1"/>
       <c r="X483" s="1"/>
       <c r="Y483" s="1"/>
-      <c r="Z483" s="1"/>
+      <c r="Z483" s="23"/>
       <c r="AA483" s="1"/>
       <c r="AB483" s="1"/>
       <c r="AC483" s="1"/>
@@ -34914,7 +34937,7 @@
       <c r="W484" s="1"/>
       <c r="X484" s="1"/>
       <c r="Y484" s="1"/>
-      <c r="Z484" s="1"/>
+      <c r="Z484" s="23"/>
       <c r="AA484" s="1"/>
       <c r="AB484" s="1"/>
       <c r="AC484" s="1"/>
@@ -34966,7 +34989,7 @@
       <c r="W485" s="1"/>
       <c r="X485" s="1"/>
       <c r="Y485" s="1"/>
-      <c r="Z485" s="1"/>
+      <c r="Z485" s="23"/>
       <c r="AA485" s="1"/>
       <c r="AB485" s="1"/>
       <c r="AC485" s="1"/>
@@ -35018,7 +35041,7 @@
       <c r="W486" s="1"/>
       <c r="X486" s="1"/>
       <c r="Y486" s="1"/>
-      <c r="Z486" s="1"/>
+      <c r="Z486" s="23"/>
       <c r="AA486" s="1"/>
       <c r="AB486" s="1"/>
       <c r="AC486" s="1"/>
@@ -35070,7 +35093,7 @@
       <c r="W487" s="1"/>
       <c r="X487" s="1"/>
       <c r="Y487" s="1"/>
-      <c r="Z487" s="1"/>
+      <c r="Z487" s="23"/>
       <c r="AA487" s="1"/>
       <c r="AB487" s="1"/>
       <c r="AC487" s="1"/>
@@ -35122,7 +35145,7 @@
       <c r="W488" s="1"/>
       <c r="X488" s="1"/>
       <c r="Y488" s="1"/>
-      <c r="Z488" s="1"/>
+      <c r="Z488" s="23"/>
       <c r="AA488" s="1"/>
       <c r="AB488" s="1"/>
       <c r="AC488" s="1"/>
@@ -35174,7 +35197,7 @@
       <c r="W489" s="1"/>
       <c r="X489" s="1"/>
       <c r="Y489" s="1"/>
-      <c r="Z489" s="1"/>
+      <c r="Z489" s="23"/>
       <c r="AA489" s="1"/>
       <c r="AB489" s="1"/>
       <c r="AC489" s="1"/>
@@ -35226,7 +35249,7 @@
       <c r="W490" s="1"/>
       <c r="X490" s="1"/>
       <c r="Y490" s="1"/>
-      <c r="Z490" s="1"/>
+      <c r="Z490" s="23"/>
       <c r="AA490" s="1"/>
       <c r="AB490" s="1"/>
       <c r="AC490" s="1"/>
@@ -35278,7 +35301,7 @@
       <c r="W491" s="1"/>
       <c r="X491" s="1"/>
       <c r="Y491" s="1"/>
-      <c r="Z491" s="1"/>
+      <c r="Z491" s="23"/>
       <c r="AA491" s="1"/>
       <c r="AB491" s="1"/>
       <c r="AC491" s="1"/>
@@ -35330,7 +35353,7 @@
       <c r="W492" s="1"/>
       <c r="X492" s="1"/>
       <c r="Y492" s="1"/>
-      <c r="Z492" s="1"/>
+      <c r="Z492" s="23"/>
       <c r="AA492" s="1"/>
       <c r="AB492" s="1"/>
       <c r="AC492" s="1"/>
@@ -35382,7 +35405,7 @@
       <c r="W493" s="1"/>
       <c r="X493" s="1"/>
       <c r="Y493" s="1"/>
-      <c r="Z493" s="1"/>
+      <c r="Z493" s="23"/>
       <c r="AA493" s="1"/>
       <c r="AB493" s="1"/>
       <c r="AC493" s="1"/>
@@ -35434,7 +35457,7 @@
       <c r="W494" s="1"/>
       <c r="X494" s="1"/>
       <c r="Y494" s="1"/>
-      <c r="Z494" s="1"/>
+      <c r="Z494" s="23"/>
       <c r="AA494" s="1"/>
       <c r="AB494" s="1"/>
       <c r="AC494" s="1"/>
@@ -35486,7 +35509,7 @@
       <c r="W495" s="1"/>
       <c r="X495" s="1"/>
       <c r="Y495" s="1"/>
-      <c r="Z495" s="1"/>
+      <c r="Z495" s="23"/>
       <c r="AA495" s="1"/>
       <c r="AB495" s="1"/>
       <c r="AC495" s="1"/>
@@ -35538,7 +35561,7 @@
       <c r="W496" s="1"/>
       <c r="X496" s="1"/>
       <c r="Y496" s="1"/>
-      <c r="Z496" s="1"/>
+      <c r="Z496" s="23"/>
       <c r="AA496" s="1"/>
       <c r="AB496" s="1"/>
       <c r="AC496" s="1"/>
@@ -35590,7 +35613,7 @@
       <c r="W497" s="1"/>
       <c r="X497" s="1"/>
       <c r="Y497" s="1"/>
-      <c r="Z497" s="1"/>
+      <c r="Z497" s="23"/>
       <c r="AA497" s="1"/>
       <c r="AB497" s="1"/>
       <c r="AC497" s="1"/>
@@ -35642,7 +35665,7 @@
       <c r="W498" s="1"/>
       <c r="X498" s="1"/>
       <c r="Y498" s="1"/>
-      <c r="Z498" s="1"/>
+      <c r="Z498" s="23"/>
       <c r="AA498" s="1"/>
       <c r="AB498" s="1"/>
       <c r="AC498" s="1"/>
@@ -35694,7 +35717,7 @@
       <c r="W499" s="1"/>
       <c r="X499" s="1"/>
       <c r="Y499" s="1"/>
-      <c r="Z499" s="1"/>
+      <c r="Z499" s="23"/>
       <c r="AA499" s="1"/>
       <c r="AB499" s="1"/>
       <c r="AC499" s="1"/>
@@ -35746,7 +35769,7 @@
       <c r="W500" s="1"/>
       <c r="X500" s="1"/>
       <c r="Y500" s="1"/>
-      <c r="Z500" s="1"/>
+      <c r="Z500" s="23"/>
       <c r="AA500" s="1"/>
       <c r="AB500" s="1"/>
       <c r="AC500" s="1"/>
@@ -35775,5 +35798,6 @@
   </sheetData>
   <autoFilter ref="A3:Y109" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>